--- a/nursing/통합간호기록_사정진단평가_260626.xlsx
+++ b/nursing/통합간호기록_사정진단평가_260626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sungkwanchoi/NFH_New/nursing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6775B5-93D9-9B4E-AD48-696257DF5B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA6BB54-FBCD-0942-8C20-8AC39E794807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14720" yWindow="680" windowWidth="14680" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="307">
   <si>
     <t>주호소 / 영역</t>
   </si>
@@ -935,6 +935,26 @@
   <si>
     <t>자살을 시도함(구체적 사항 기재)</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도관 — 수술부위</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">수술상처 출혈 있음 </t>
+  </si>
+  <si>
+    <t>수술상처 출혈 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수술상처 dressing 상태임 </t>
+  </si>
+  <si>
+    <t>도관 — 상처부위</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">상처 dressing 상태임 </t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E264"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1510,7 +1530,9 @@
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C10" s="8" t="s">
         <v>281</v>
       </c>
@@ -1520,7 +1542,9 @@
       <c r="A11" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="8" t="s">
         <v>279</v>
       </c>
@@ -1624,43 +1648,40 @@
     </row>
     <row r="20" spans="1:5" ht="18">
       <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" spans="1:5" ht="18">
       <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>28</v>
+        <v>301</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>304</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="18">
       <c r="A22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="4" t="s">
-        <v>5</v>
+        <v>301</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18">
@@ -1671,10 +1692,10 @@
         <v>25</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18">
@@ -1685,225 +1706,224 @@
         <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:5" ht="18">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="36">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="18">
       <c r="A33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18">
+      <c r="A34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="36">
-      <c r="A34" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="B34" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="36">
       <c r="A35" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" ht="18">
       <c r="A36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="36">
       <c r="A37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="36">
+      <c r="A38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38" spans="1:4" ht="18">
-      <c r="A38" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="B38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>62</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" ht="18">
       <c r="A39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="18">
+        <v>57</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" ht="36">
       <c r="A40" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" ht="18">
       <c r="A41" s="2" t="s">
@@ -1913,9 +1933,11 @@
         <v>25</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D41" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="18">
       <c r="A42" s="2" t="s">
@@ -1925,9 +1947,11 @@
         <v>25</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="18">
       <c r="A43" s="2" t="s">
@@ -1937,19 +1961,21 @@
         <v>25</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="18">
       <c r="A44" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>56</v>
+      <c r="B44" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -1957,11 +1983,11 @@
       <c r="A45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>58</v>
+      <c r="B45" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D45" s="2"/>
     </row>
@@ -1969,11 +1995,11 @@
       <c r="A46" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>58</v>
+      <c r="B46" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -1985,7 +2011,7 @@
         <v>56</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -1997,7 +2023,7 @@
         <v>58</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -2009,7 +2035,7 @@
         <v>58</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -2021,7 +2047,7 @@
         <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -2033,7 +2059,7 @@
         <v>58</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -2045,7 +2071,7 @@
         <v>58</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -2053,11 +2079,11 @@
       <c r="A53" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>58</v>
+      <c r="B53" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -2069,7 +2095,7 @@
         <v>58</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -2077,11 +2103,11 @@
       <c r="A55" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>56</v>
+      <c r="B55" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -2093,7 +2119,7 @@
         <v>58</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -2105,7 +2131,7 @@
         <v>58</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -2113,55 +2139,49 @@
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>58</v>
+      <c r="B58" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" ht="18">
       <c r="A59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>80</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" ht="18">
       <c r="A60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" ht="18">
       <c r="A61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" ht="18">
       <c r="A62" s="2" t="s">
@@ -2171,10 +2191,10 @@
         <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18">
@@ -2185,10 +2205,10 @@
         <v>25</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18">
@@ -2199,9 +2219,11 @@
         <v>25</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="65" spans="1:4" ht="18">
       <c r="A65" s="2" t="s">
@@ -2211,9 +2233,11 @@
         <v>25</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D65" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="66" spans="1:4" ht="18">
       <c r="A66" s="2" t="s">
@@ -2223,21 +2247,21 @@
         <v>25</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18">
       <c r="A67" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>56</v>
+      <c r="B67" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -2245,11 +2269,11 @@
       <c r="A68" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>58</v>
+      <c r="B68" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -2257,13 +2281,15 @@
       <c r="A69" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>58</v>
+      <c r="B69" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D69" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="70" spans="1:4" ht="18">
       <c r="A70" s="2" t="s">
@@ -2273,7 +2299,7 @@
         <v>56</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -2291,45 +2317,39 @@
     </row>
     <row r="72" spans="1:4" ht="18">
       <c r="A72" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" ht="18">
       <c r="A73" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" ht="18">
       <c r="A74" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" ht="18">
       <c r="A75" s="2" t="s">
@@ -2339,10 +2359,10 @@
         <v>25</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="18">
@@ -2352,58 +2372,64 @@
       <c r="B76" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>290</v>
+      <c r="C76" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18">
       <c r="A77" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>56</v>
+      <c r="B77" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D77" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="18">
       <c r="A78" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>58</v>
+      <c r="B78" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="79" spans="1:4" ht="18">
       <c r="A79" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>58</v>
+      <c r="B79" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D79" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="80" spans="1:4" ht="18">
       <c r="A80" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>58</v>
+      <c r="B80" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -2411,11 +2437,11 @@
       <c r="A81" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>56</v>
+      <c r="B81" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -2426,8 +2452,8 @@
       <c r="B82" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>105</v>
+      <c r="C82" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -2438,8 +2464,8 @@
       <c r="B83" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>288</v>
+      <c r="C83" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -2447,11 +2473,11 @@
       <c r="A84" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>58</v>
+      <c r="B84" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -2459,11 +2485,11 @@
       <c r="A85" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>56</v>
+      <c r="B85" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -2474,8 +2500,8 @@
       <c r="B86" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>106</v>
+      <c r="C86" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -2486,8 +2512,8 @@
       <c r="B87" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>288</v>
+      <c r="C87" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -2495,51 +2521,47 @@
       <c r="A88" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>58</v>
+      <c r="B88" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89" spans="1:4" ht="18">
       <c r="A89" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D89" s="2"/>
     </row>
     <row r="90" spans="1:4" ht="18">
       <c r="A90" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>111</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D90" s="2"/>
     </row>
     <row r="91" spans="1:4" ht="18">
       <c r="A91" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>25</v>
+        <v>95</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -2551,33 +2573,35 @@
         <v>25</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="18">
       <c r="A93" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>56</v>
+      <c r="B93" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D93" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="18">
       <c r="A94" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>58</v>
+      <c r="B94" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -2585,13 +2609,15 @@
       <c r="A95" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>58</v>
+      <c r="B95" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="96" spans="1:4" ht="18">
       <c r="A96" s="2" t="s">
@@ -2601,7 +2627,7 @@
         <v>56</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -2613,7 +2639,7 @@
         <v>58</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -2624,46 +2650,44 @@
       <c r="B98" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>292</v>
+      <c r="C98" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99" spans="1:4" ht="18">
       <c r="A99" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>25</v>
+        <v>109</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100" spans="1:4" ht="18">
       <c r="A100" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>294</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D100" s="2"/>
     </row>
     <row r="101" spans="1:4" ht="18">
       <c r="A101" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -2675,11 +2699,9 @@
         <v>25</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>123</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D102" s="2"/>
     </row>
     <row r="103" spans="1:4" ht="18">
       <c r="A103" s="2" t="s">
@@ -2688,10 +2710,12 @@
       <c r="B103" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D103" s="2"/>
+      <c r="C103" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="104" spans="1:4" ht="18">
       <c r="A104" s="2" t="s">
@@ -2701,7 +2725,7 @@
         <v>25</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -2709,23 +2733,25 @@
       <c r="A105" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>56</v>
+      <c r="B105" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D105" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="106" spans="1:4" ht="18">
       <c r="A106" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>58</v>
+      <c r="B106" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -2733,11 +2759,11 @@
       <c r="A107" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>58</v>
+      <c r="B107" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -2749,7 +2775,7 @@
         <v>56</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -2773,7 +2799,7 @@
         <v>58</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -2785,7 +2811,7 @@
         <v>56</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -2797,7 +2823,7 @@
         <v>58</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -2809,7 +2835,7 @@
         <v>58</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -2817,11 +2843,11 @@
       <c r="A114" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>58</v>
+      <c r="B114" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -2832,8 +2858,8 @@
       <c r="B115" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>295</v>
+      <c r="C115" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -2845,7 +2871,7 @@
         <v>58</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -2853,11 +2879,11 @@
       <c r="A117" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B117" s="7" t="s">
-        <v>56</v>
+      <c r="B117" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -2868,8 +2894,8 @@
       <c r="B118" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>137</v>
+      <c r="C118" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -2880,8 +2906,8 @@
       <c r="B119" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>295</v>
+      <c r="C119" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -2889,11 +2915,11 @@
       <c r="A120" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>58</v>
+      <c r="B120" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -2905,51 +2931,45 @@
         <v>58</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122" spans="1:4" ht="18">
       <c r="A122" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D122" s="2"/>
     </row>
     <row r="123" spans="1:4" ht="18">
       <c r="A123" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>25</v>
+        <v>119</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D123" s="2"/>
     </row>
     <row r="124" spans="1:4" ht="18">
       <c r="A124" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>25</v>
+        <v>119</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D124" s="2"/>
     </row>
     <row r="125" spans="1:4" ht="18">
       <c r="A125" s="2" t="s">
@@ -2959,10 +2979,10 @@
         <v>25</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18">
@@ -2973,43 +2993,49 @@
         <v>25</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D126" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="127" spans="1:4" ht="18">
       <c r="A127" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B127" s="7" t="s">
-        <v>56</v>
+      <c r="B127" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D127" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="128" spans="1:4" ht="18">
       <c r="A128" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>58</v>
+      <c r="B128" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D128" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="129" spans="1:4" ht="18">
       <c r="A129" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>58</v>
+      <c r="B129" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -3017,51 +3043,47 @@
       <c r="A130" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>58</v>
+      <c r="B130" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131" spans="1:4" ht="18">
       <c r="A131" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>25</v>
+        <v>139</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D131" s="2"/>
     </row>
     <row r="132" spans="1:4" ht="18">
       <c r="A132" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>25</v>
+        <v>139</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="D132" s="2"/>
     </row>
     <row r="133" spans="1:4" ht="18">
       <c r="A133" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>25</v>
+        <v>139</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -3073,10 +3095,10 @@
         <v>25</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="18">
@@ -3087,10 +3109,10 @@
         <v>25</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="18">
@@ -3101,97 +3123,97 @@
         <v>25</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>164</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" spans="1:4" ht="18">
       <c r="A137" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B137" s="7" t="s">
-        <v>56</v>
+      <c r="B137" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D137" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="138" spans="1:4" ht="18">
       <c r="A138" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>58</v>
+      <c r="B138" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D138" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="139" spans="1:4" ht="18">
       <c r="A139" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>58</v>
+      <c r="B139" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D139" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="140" spans="1:4" ht="18">
       <c r="A140" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>58</v>
+      <c r="B140" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141" spans="1:4" ht="18">
       <c r="A141" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D141" s="2"/>
     </row>
     <row r="142" spans="1:4" ht="18">
       <c r="A142" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D142" s="2"/>
     </row>
     <row r="143" spans="1:4" ht="18">
       <c r="A143" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>25</v>
+        <v>153</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>298</v>
+        <v>166</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -3203,9 +3225,11 @@
         <v>25</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D144" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="145" spans="1:5" ht="18">
       <c r="A145" s="2" t="s">
@@ -3215,10 +3239,10 @@
         <v>25</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="18">
@@ -3229,11 +3253,9 @@
         <v>25</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" spans="1:5" ht="18">
       <c r="A147" s="2" t="s">
@@ -3243,11 +3265,9 @@
         <v>25</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>169</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" spans="1:5" ht="18">
       <c r="A148" s="2" t="s">
@@ -3257,10 +3277,10 @@
         <v>25</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="18">
@@ -3271,57 +3291,63 @@
         <v>25</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="18">
       <c r="A150" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B150" s="7" t="s">
-        <v>56</v>
+      <c r="B150" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D150" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="151" spans="1:5" ht="18">
       <c r="A151" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>58</v>
+      <c r="B151" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D151" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="152" spans="1:5" ht="18">
       <c r="A152" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B152" s="3" t="s">
-        <v>58</v>
+      <c r="B152" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D152" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="153" spans="1:5" ht="18">
       <c r="A153" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B153" s="3" t="s">
-        <v>58</v>
+      <c r="B153" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -3333,54 +3359,45 @@
         <v>58</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155" spans="1:5" ht="18">
       <c r="A155" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>25</v>
+        <v>167</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>296</v>
+        <v>176</v>
       </c>
       <c r="D155" s="2"/>
-      <c r="E155" s="4" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="156" spans="1:5" ht="18">
       <c r="A156" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>25</v>
+        <v>167</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E156" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" spans="1:5" ht="18">
       <c r="A157" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>25</v>
+        <v>167</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E157" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="D157" s="2"/>
     </row>
     <row r="158" spans="1:5" ht="18">
       <c r="A158" s="2" t="s">
@@ -3390,10 +3407,12 @@
         <v>25</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>28</v>
+        <v>296</v>
       </c>
       <c r="D158" s="2"/>
-      <c r="E158" s="4"/>
+      <c r="E158" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="159" spans="1:5" ht="18">
       <c r="A159" s="2" t="s">
@@ -3403,9 +3422,11 @@
         <v>25</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D159" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="E159" s="4"/>
     </row>
     <row r="160" spans="1:5" ht="18">
@@ -3416,10 +3437,10 @@
         <v>25</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E160" s="4"/>
     </row>
@@ -3431,11 +3452,9 @@
         <v>25</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D161" s="2"/>
       <c r="E161" s="4"/>
     </row>
     <row r="162" spans="1:5" ht="18">
@@ -3446,57 +3465,64 @@
         <v>25</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D162" s="2"/>
+      <c r="E162" s="4"/>
     </row>
     <row r="163" spans="1:5" ht="18">
       <c r="A163" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B163" s="7" t="s">
-        <v>56</v>
+      <c r="B163" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D163" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E163" s="4"/>
     </row>
     <row r="164" spans="1:5" ht="18">
       <c r="A164" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>58</v>
+      <c r="B164" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D164" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E164" s="4"/>
     </row>
     <row r="165" spans="1:5" ht="18">
       <c r="A165" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>58</v>
+      <c r="B165" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D165" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="166" spans="1:5" ht="18">
       <c r="A166" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>58</v>
+      <c r="B166" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -3508,49 +3534,45 @@
         <v>58</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>291</v>
+        <v>180</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168" spans="1:5" ht="18">
       <c r="A168" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>25</v>
+        <v>178</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169" spans="1:5" ht="18">
       <c r="A169" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>25</v>
+        <v>178</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>185</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D169" s="2"/>
     </row>
     <row r="170" spans="1:5" ht="18">
       <c r="A170" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>25</v>
+        <v>178</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="D170" s="2"/>
     </row>
     <row r="171" spans="1:5" ht="18">
       <c r="A171" s="2" t="s">
@@ -3560,11 +3582,9 @@
         <v>25</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" spans="1:5" ht="18">
       <c r="A172" s="2" t="s">
@@ -3574,47 +3594,53 @@
         <v>25</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="18">
       <c r="A173" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B173" s="7" t="s">
-        <v>56</v>
+      <c r="B173" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D173" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="174" spans="1:5" ht="18">
       <c r="A174" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>58</v>
+      <c r="B174" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D174" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="175" spans="1:5" ht="18">
       <c r="A175" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B175" s="3" t="s">
-        <v>58</v>
+      <c r="B175" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D175" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="176" spans="1:5" ht="18">
       <c r="A176" s="2" t="s">
@@ -3624,7 +3650,7 @@
         <v>56</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -3636,51 +3662,45 @@
         <v>58</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178" spans="1:4" ht="18">
       <c r="A178" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>25</v>
+        <v>182</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>197</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D178" s="2"/>
     </row>
     <row r="179" spans="1:4" ht="18">
       <c r="A179" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>25</v>
+        <v>182</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="D179" s="2"/>
     </row>
     <row r="180" spans="1:4" ht="18">
       <c r="A180" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>25</v>
+        <v>182</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>201</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="D180" s="2"/>
     </row>
     <row r="181" spans="1:4" ht="18">
       <c r="A181" s="2" t="s">
@@ -3690,10 +3710,10 @@
         <v>25</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="18">
@@ -3704,9 +3724,11 @@
         <v>25</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D182" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="183" spans="1:4" ht="18">
       <c r="A183" s="2" t="s">
@@ -3716,33 +3738,35 @@
         <v>25</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="18">
       <c r="A184" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B184" s="7" t="s">
-        <v>56</v>
+      <c r="B184" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D184" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="185" spans="1:4" ht="18">
       <c r="A185" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B185" s="3" t="s">
-        <v>58</v>
+      <c r="B185" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -3750,13 +3774,15 @@
       <c r="A186" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B186" s="3" t="s">
-        <v>58</v>
+      <c r="B186" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D186" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="187" spans="1:4" ht="18">
       <c r="A187" s="2" t="s">
@@ -3766,7 +3792,7 @@
         <v>56</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -3778,7 +3804,7 @@
         <v>58</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -3790,7 +3816,7 @@
         <v>58</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -3802,7 +3828,7 @@
         <v>56</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -3814,7 +3840,7 @@
         <v>58</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -3826,87 +3852,87 @@
         <v>58</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193" spans="1:4" ht="18">
       <c r="A193" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>25</v>
+        <v>195</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>214</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D193" s="2"/>
     </row>
     <row r="194" spans="1:4" ht="18">
       <c r="A194" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>25</v>
+        <v>195</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="D194" s="2"/>
     </row>
     <row r="195" spans="1:4" ht="18">
       <c r="A195" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>25</v>
+        <v>195</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D195" s="2"/>
     </row>
     <row r="196" spans="1:4" ht="18">
       <c r="A196" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B196" s="7" t="s">
-        <v>56</v>
+      <c r="B196" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D196" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="197" spans="1:4" ht="18">
       <c r="A197" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B197" s="3" t="s">
-        <v>58</v>
+      <c r="B197" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D197" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="198" spans="1:4" ht="18">
       <c r="A198" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B198" s="3" t="s">
-        <v>58</v>
+      <c r="B198" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D198" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="199" spans="1:4" ht="18">
       <c r="A199" s="2" t="s">
@@ -3916,7 +3942,7 @@
         <v>56</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -3928,45 +3954,43 @@
         <v>58</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201" spans="1:4" ht="18">
       <c r="A201" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>25</v>
+        <v>212</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" spans="1:4" ht="18">
       <c r="A202" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>25</v>
+        <v>212</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203" spans="1:4" ht="18">
       <c r="A203" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>25</v>
+        <v>212</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -3978,10 +4002,10 @@
         <v>25</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="18">
@@ -3992,11 +4016,9 @@
         <v>25</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D205" s="2"/>
     </row>
     <row r="206" spans="1:4" ht="18">
       <c r="A206" s="2" t="s">
@@ -4006,11 +4028,9 @@
         <v>25</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D206" s="2"/>
     </row>
     <row r="207" spans="1:4" ht="18">
       <c r="A207" s="2" t="s">
@@ -4020,10 +4040,10 @@
         <v>25</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>228</v>
+        <v>30</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>229</v>
+        <v>31</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="18">
@@ -4034,10 +4054,10 @@
         <v>25</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>225</v>
+        <v>32</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="18">
@@ -4048,10 +4068,10 @@
         <v>25</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="18">
@@ -4062,47 +4082,53 @@
         <v>25</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="18">
       <c r="A211" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B211" s="7" t="s">
-        <v>56</v>
+      <c r="B211" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D211" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="212" spans="1:4" ht="18">
       <c r="A212" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B212" s="3" t="s">
-        <v>58</v>
+      <c r="B212" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D212" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="213" spans="1:4" ht="18">
       <c r="A213" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B213" s="3" t="s">
-        <v>58</v>
+      <c r="B213" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D213" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="214" spans="1:4" ht="18">
       <c r="A214" s="2" t="s">
@@ -4112,7 +4138,7 @@
         <v>56</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -4124,7 +4150,7 @@
         <v>58</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -4136,7 +4162,7 @@
         <v>58</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -4144,53 +4170,51 @@
       <c r="A217" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B217" s="3" t="s">
-        <v>58</v>
+      <c r="B217" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218" spans="1:4" ht="18">
       <c r="A218" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>25</v>
+        <v>224</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="D218" s="2"/>
     </row>
     <row r="219" spans="1:4" ht="18">
       <c r="A219" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C219" s="8" t="s">
-        <v>300</v>
+        <v>224</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220" spans="1:4" ht="18">
       <c r="A220" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C220" s="8" t="s">
-        <v>299</v>
+        <v>224</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D220" s="2"/>
     </row>
-    <row r="221" spans="1:4" ht="36">
+    <row r="221" spans="1:4" ht="18">
       <c r="A221" s="2" t="s">
         <v>239</v>
       </c>
@@ -4198,10 +4222,10 @@
         <v>25</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="18">
@@ -4211,48 +4235,50 @@
       <c r="B222" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C222" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="C222" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D222" s="2"/>
     </row>
     <row r="223" spans="1:4" ht="18">
       <c r="A223" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B223" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>246</v>
+      <c r="B223" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="D223" s="2"/>
     </row>
-    <row r="224" spans="1:4" ht="18">
+    <row r="224" spans="1:4" ht="36">
       <c r="A224" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>58</v>
+      <c r="B224" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D224" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="225" spans="1:5" ht="18">
       <c r="A225" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>58</v>
+      <c r="B225" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D225" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="226" spans="1:5" ht="18">
       <c r="A226" s="2" t="s">
@@ -4262,7 +4288,7 @@
         <v>56</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -4274,7 +4300,7 @@
         <v>58</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -4286,7 +4312,7 @@
         <v>58</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -4298,7 +4324,7 @@
         <v>56</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -4310,7 +4336,7 @@
         <v>58</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -4322,45 +4348,43 @@
         <v>58</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232" spans="1:5" ht="18">
       <c r="A232" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>25</v>
+        <v>239</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="D232" s="2"/>
     </row>
     <row r="233" spans="1:5" ht="18">
       <c r="A233" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>25</v>
+        <v>239</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234" spans="1:5" ht="18">
       <c r="A234" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>25</v>
+        <v>239</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>29</v>
+        <v>253</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -4372,10 +4396,10 @@
         <v>25</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="18">
@@ -4386,11 +4410,9 @@
         <v>25</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D236" s="2"/>
     </row>
     <row r="237" spans="1:5" ht="18">
       <c r="A237" s="2" t="s">
@@ -4400,14 +4422,9 @@
         <v>25</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E237" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D237" s="2"/>
     </row>
     <row r="238" spans="1:5" ht="18">
       <c r="A238" s="2" t="s">
@@ -4417,47 +4434,56 @@
         <v>25</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>255</v>
+        <v>30</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>256</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="18">
       <c r="A239" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B239" s="7" t="s">
-        <v>56</v>
+      <c r="B239" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D239" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="240" spans="1:5" ht="18">
       <c r="A240" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B240" s="3" t="s">
-        <v>58</v>
+      <c r="B240" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D240" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E240" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="241" spans="1:4" ht="18">
       <c r="A241" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B241" s="3" t="s">
-        <v>58</v>
+      <c r="B241" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D241" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="242" spans="1:4" ht="18">
       <c r="A242" s="2" t="s">
@@ -4467,7 +4493,7 @@
         <v>56</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -4479,7 +4505,7 @@
         <v>58</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -4491,51 +4517,45 @@
         <v>58</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245" spans="1:4" ht="18">
       <c r="A245" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>25</v>
+        <v>254</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D245" s="2"/>
     </row>
     <row r="246" spans="1:4" ht="18">
       <c r="A246" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>25</v>
+        <v>254</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>261</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="D246" s="2"/>
     </row>
     <row r="247" spans="1:4" ht="18">
       <c r="A247" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>25</v>
+        <v>254</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>263</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D247" s="2"/>
     </row>
     <row r="248" spans="1:4" ht="18">
       <c r="A248" s="2" t="s">
@@ -4545,43 +4565,49 @@
         <v>25</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D248" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="249" spans="1:4" ht="18">
       <c r="A249" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B249" s="7" t="s">
-        <v>56</v>
+      <c r="B249" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D249" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="250" spans="1:4" ht="18">
       <c r="A250" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B250" s="3" t="s">
-        <v>58</v>
+      <c r="B250" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D250" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="251" spans="1:4" ht="18">
       <c r="A251" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B251" s="3" t="s">
-        <v>58</v>
+      <c r="B251" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>133</v>
+        <v>264</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -4589,47 +4615,47 @@
       <c r="A252" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B252" s="3" t="s">
-        <v>58</v>
+      <c r="B252" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253" spans="1:4" ht="18">
       <c r="A253" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>25</v>
+        <v>259</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254" spans="1:4" ht="18">
       <c r="A254" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>25</v>
+        <v>259</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>270</v>
+        <v>133</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255" spans="1:4" ht="18">
       <c r="A255" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>25</v>
+        <v>259</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -4641,7 +4667,7 @@
         <v>25</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -4653,7 +4679,7 @@
         <v>25</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -4661,11 +4687,11 @@
       <c r="A258" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B258" s="7" t="s">
-        <v>56</v>
+      <c r="B258" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -4673,11 +4699,11 @@
       <c r="A259" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B259" s="3" t="s">
-        <v>58</v>
+      <c r="B259" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>176</v>
+        <v>271</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -4685,11 +4711,11 @@
       <c r="A260" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B260" s="3" t="s">
-        <v>58</v>
+      <c r="B260" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -4697,13 +4723,49 @@
       <c r="A261" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B261" s="3" t="s">
-        <v>58</v>
+      <c r="B261" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C261" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D261" s="2"/>
+    </row>
+    <row r="262" spans="1:4" ht="18">
+      <c r="A262" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D262" s="2"/>
+    </row>
+    <row r="263" spans="1:4" ht="18">
+      <c r="A263" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D263" s="2"/>
+    </row>
+    <row r="264" spans="1:4" ht="18">
+      <c r="A264" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D261" s="2"/>
+      <c r="D264" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/nursing/통합간호기록_사정진단평가_260626.xlsx
+++ b/nursing/통합간호기록_사정진단평가_260626.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2936,15 +2936,20 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈중 나트륨(Na) 높음</t>
+          <t>🩺 근력 감소 (위약감)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이상임</t>
+          <t>근력 감소함</t>
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -2959,15 +2964,20 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈중 나트륨(Na) 낮음</t>
+          <t>🩺 기면 (자꾸 졸고 처짐)</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이하임</t>
+          <t>lethargy 상태임</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -2975,18 +2985,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n"/>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>"변비가 있으세요?"</t>
+        </is>
+      </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>변비 있음</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -2994,18 +3013,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n"/>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>복부 통증 있음</t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -3013,18 +3041,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n"/>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>"소변을 자주 보고 목이 마르세요?"</t>
+        </is>
+      </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 인슐린 투여함</t>
+          <t>다뇨증 있음</t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -3032,18 +3069,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>🩺 심전도 QT 간격 단축 (고칼슘)</t>
+        </is>
+      </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>QT 간격 짧아짐</t>
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -3051,18 +3097,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n"/>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>🩺 Chvostek 징후 — 귀 앞쪽 뺨(안면신경)을 손가락으로 톡톡 두드렸을 때 입꼬리·얼굴이 씰룩이면 양성</t>
+        </is>
+      </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>Chvostek sign 있음</t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -3070,18 +3125,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n"/>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>🩺 Trousseau 징후 — 혈압계 커프를 수축기압보다 20mmHg 높여 3분 유지했을 때 손목·손가락이 굽고 뻣뻣해지면 양성</t>
+        </is>
+      </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 D50W 을 투여함</t>
+          <t>Trousseau's sign 있음</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -3089,18 +3153,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>🩺 수족 경련(carpopedal spasm) — 손목·발목이 안쪽으로 굽으며 뻣뻣하게 경련함</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>고칼륨혈증</t>
+          <t>carpopedal spasm 있음</t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -3108,18 +3181,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n"/>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>"입술이나 입 주위가 저리거나 얼얼하세요?"</t>
+        </is>
+      </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>hyperkalemia 증상이 있는지 확인함</t>
+          <t>Perioral numbness</t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -3127,18 +3209,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n"/>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>"손발이 저리세요?"</t>
+        </is>
+      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>이상감각 있음</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -3146,18 +3237,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n"/>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>🩺 심전도 QT 간격 연장 (저칼슘)</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 제한하도록 교육함</t>
+          <t>QT 간격 연장되어 있음</t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -3165,18 +3265,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n"/>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>🩺 부정맥 (불규칙한 맥박)</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>혈중 potassium  검사결과 확인함</t>
+          <t>부정맥 있음</t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -3184,15 +3293,19 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n"/>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈중 나트륨(Na) 높음</t>
+        </is>
+      </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
+          <t>혈중 sodium 수치 정상 이상임</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
@@ -3203,15 +3316,19 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n"/>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈중 나트륨(Na) 낮음</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>혈중 sodium 수치 정상 이하임</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
@@ -3222,18 +3339,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n"/>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>"갈증이 많이 나세요?"</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>hypokalemia 증상이 있는지 확인함</t>
+          <t>갈증 있음</t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -3241,18 +3367,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>🩺 소변량 감소·핍뇨</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>혈중 potassium  검사결과 확인함</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -3260,18 +3395,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n"/>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>🩺 의식수준 저하 (처지고 반응이 둔함)</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>의식수준 저하됨</t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -3279,18 +3423,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n"/>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>🩺 경련·발작 보임</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 격려함</t>
+          <t>경련 있음</t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -3298,18 +3451,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n"/>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>"머리가 아프세요?"</t>
+        </is>
+      </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>고칼슘혈증</t>
+          <t>두통 있음</t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -3317,18 +3479,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n"/>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>"메스껍거나 토하세요?"</t>
+        </is>
+      </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>hypercalcemia 증상이 있는지 확인함</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -3336,18 +3507,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n"/>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>"기운이 없고 축 처지세요?"</t>
+        </is>
+      </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>혈중 calcium 검사결과 확인함</t>
+          <t>무기력 호소함</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -3355,15 +3535,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>칼슘 섭취를 제한하도록 함</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -3374,15 +3554,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>저칼슘혈증</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
@@ -3401,7 +3581,7 @@
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>hypocalcemia 증상이 있는지 확인함</t>
+          <t>처방에 의해 인슐린 투여함</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -3412,15 +3592,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>혈중 calcium 검사결과 확인함</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -3439,7 +3619,7 @@
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Calcium gluconate 를 투여함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -3450,15 +3630,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>고나트륨혈증</t>
+          <t>처방에 의해 D50W 을 투여함</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -3469,15 +3649,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>hypernatremia의 증상이 있는지 확인함</t>
+          <t>고칼륨혈증</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -3496,7 +3676,7 @@
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>hyperkalemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -3507,15 +3687,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>저나트륨혈증</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -3534,7 +3714,7 @@
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>hyponatremia 증상이 있는지 확인함</t>
+          <t>고칼륨식이 섭취 제한하도록 교육함</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -3553,7 +3733,7 @@
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>혈중 potassium  검사결과 확인함</t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -3572,7 +3752,7 @@
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>sodium 섭취를 늘리도록 교육함</t>
+          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
@@ -3583,15 +3763,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
@@ -3599,130 +3779,94 @@
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>"소변보기 힘드세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>배뇨곤란 있음</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>배뇨곤란 없음</t>
-        </is>
-      </c>
+          <t>hypokalemia 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>"소변이 막힌 느낌이세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>요정체 있음</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>요정체 없음</t>
-        </is>
-      </c>
+          <t>혈중 potassium  검사결과 확인함</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>잔뇨감 있음</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>잔뇨감 없음</t>
-        </is>
-      </c>
+          <t>EKG monitor 시작함</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>"소변에 피가 보이나요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>혈뇨 있음</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>혈뇨 없음</t>
-        </is>
-      </c>
+          <t>고칼륨식이 섭취 격려함</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>🩺 소변량 감소</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>고칼슘혈증</t>
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
@@ -3730,18 +3874,18 @@
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>hypercalcemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
@@ -3749,7 +3893,7 @@
     <row r="151" ht="36" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -3760,7 +3904,7 @@
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
+          <t>혈중 calcium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
@@ -3768,7 +3912,7 @@
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -3779,7 +3923,7 @@
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>단순도뇨 시행함</t>
+          <t>칼슘 섭취를 제한하도록 함</t>
         </is>
       </c>
       <c r="E152" s="2" t="n"/>
@@ -3787,18 +3931,18 @@
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>저칼슘혈증</t>
         </is>
       </c>
       <c r="E153" s="2" t="n"/>
@@ -3806,76 +3950,56 @@
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>"귀에서 분비물이 나오세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>귀분비물 있음</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>귀분비물 없음</t>
-        </is>
-      </c>
+          <t>hypocalcemia 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>"귀울림(이명)이 있으세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>이명 있음</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>이명 없음</t>
-        </is>
-      </c>
+          <t>혈중 calcium 검사결과 확인함</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>"잘 안 들리세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>청력 이상 있음</t>
+          <t>처방에 의해 Calcium gluconate 를 투여함</t>
         </is>
       </c>
       <c r="E156" s="2" t="n"/>
@@ -3883,88 +4007,64 @@
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>"코가 막히세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>코막힘 있음</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>코막힘 없음</t>
-        </is>
-      </c>
+          <t>고나트륨혈증</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>"콧물이 나세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>콧물 있음</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>콧물 없음</t>
-        </is>
-      </c>
+          <t>hypernatremia의 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>"삼키기 힘드세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>연하곤란 있음</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>연하곤란 없음</t>
-        </is>
-      </c>
+          <t>혈중 sodium 검사결과 확인함</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
@@ -3975,7 +4075,7 @@
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>저나트륨혈증</t>
         </is>
       </c>
       <c r="E160" s="2" t="n"/>
@@ -3983,7 +4083,7 @@
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -3994,7 +4094,7 @@
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>hyponatremia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E161" s="2" t="n"/>
@@ -4002,7 +4102,7 @@
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -4013,7 +4113,7 @@
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>청력장애가 있는지 사정함</t>
+          <t>혈중 sodium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E162" s="2" t="n"/>
@@ -4021,7 +4121,7 @@
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>🍬 혈당·전해질</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -4032,7 +4132,7 @@
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+          <t>sodium 섭취를 늘리도록 교육함</t>
         </is>
       </c>
       <c r="E163" s="2" t="n"/>
@@ -4040,34 +4140,26 @@
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>오심, 구토 없음</t>
-        </is>
-      </c>
+          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -4077,24 +4169,24 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"소변보기 힘드세요?"</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
+          <t>배뇨곤란 있음</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>dizziness 없음</t>
+          <t>배뇨곤란 없음</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4104,25 +4196,24 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>"소변이 막힌 느낌이세요?"</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="n"/>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>요정체 있음</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>요정체 없음</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4132,25 +4223,24 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="n"/>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>잔뇨감 있음</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>잔뇨감 없음</t>
         </is>
       </c>
     </row>
     <row r="168" ht="36" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -4160,24 +4250,24 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"소변에 피가 보이나요?"</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
+          <t>혈뇨 있음</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>감각이상 없음</t>
+          <t>혈뇨 없음</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -4187,116 +4277,88 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>🩺 소변량 감소</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>vertigo 있음</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>vertigo 없음</t>
-        </is>
-      </c>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n"/>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>syncope 있음</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>syncope 없음</t>
-        </is>
-      </c>
+          <t>요정체가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
-        </is>
-      </c>
+          <t>단순도뇨 시행함</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>혈뇨가 있는지 확인함</t>
         </is>
       </c>
       <c r="E173" s="2" t="n"/>
@@ -4304,56 +4366,76 @@
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>"귀에서 분비물이 나오세요?"</t>
+        </is>
+      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="n"/>
+          <t>귀분비물 있음</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>귀분비물 없음</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>"귀울림(이명)이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="n"/>
+          <t>이명 있음</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>이명 없음</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>"잘 안 들리세요?"</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>청력 이상 있음</t>
         </is>
       </c>
       <c r="E176" s="2" t="n"/>
@@ -4361,75 +4443,99 @@
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>"코가 막히세요?"</t>
+        </is>
+      </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="n"/>
+          <t>코막힘 있음</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>코막힘 없음</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>"콧물이 나세요?"</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="n"/>
+          <t>콧물 있음</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>콧물 없음</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>"삼키기 힘드세요?"</t>
+        </is>
+      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="n"/>
+          <t>연하곤란 있음</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>연하곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C180" s="2" t="n"/>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>조직관류 증진 방법에 대해 교육함</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="E180" s="2" t="n"/>
@@ -4437,7 +4543,7 @@
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
@@ -4448,7 +4554,7 @@
       <c r="C181" s="2" t="n"/>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E181" s="2" t="n"/>
@@ -4456,62 +4562,45 @@
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>음독 함 ★</t>
+          <t>청력장애가 있는지 사정함</t>
         </is>
       </c>
       <c r="E182" s="2" t="n"/>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>★칩스확정</t>
-        </is>
-      </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>"토하셨어요?"</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n"/>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>오심, 구토 없음</t>
-        </is>
-      </c>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -4521,24 +4610,24 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>dizziness 없음</t>
+          <t>오심, 구토 없음</t>
         </is>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -4548,25 +4637,24 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="n"/>
-      <c r="F185" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>dizziness 있음</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -4576,12 +4664,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
         </is>
       </c>
       <c r="E186" s="2" t="n"/>
@@ -4594,7 +4682,7 @@
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -4604,24 +4692,25 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -4631,24 +4720,24 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
+          <t>감각이상 있음</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함</t>
+          <t>감각이상 없음</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -4658,92 +4747,116 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
+          <t>grasp power 약함</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능함</t>
+          <t>grasp power 강함</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>중독위험</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="n"/>
+          <t>vertigo 있음</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>vertigo 없음</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B191" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>위세척에 대해 설명함</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="n"/>
+          <t>syncope 있음</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>syncope 없음</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B192" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 해독제를 투여함</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B193" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E193" s="2" t="n"/>
@@ -4751,7 +4864,7 @@
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -4762,7 +4875,7 @@
       <c r="C194" s="2" t="n"/>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
@@ -4770,22 +4883,18 @@
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>"부러진 곳(골절)이 있으세요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>골절 있음</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E195" s="2" t="n"/>
@@ -4793,126 +4902,94 @@
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>"다친 곳이 붓나요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>골절부위 edema 있음</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>골절부위 edema 없음</t>
-        </is>
-      </c>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>"저릿하거나 감각이 이상하세요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>골절부위 tingling sense 있음</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>골절부위 tingling sense 없음</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n"/>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>찰과상 있음</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>찰과상 없음</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>"피가 나나요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n"/>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>출혈 있음</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>출혈 없음</t>
-        </is>
-      </c>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C200" s="2" t="n"/>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>조직관류 증진 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E200" s="2" t="n"/>
@@ -4920,7 +4997,7 @@
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -4931,7 +5008,7 @@
       <c r="C201" s="2" t="n"/>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>골절부위 압박붕대 감아줌</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E201" s="2" t="n"/>
@@ -4939,64 +5016,89 @@
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B202" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+        </is>
+      </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>골절부위 올려줌</t>
+          <t>음독 함 ★</t>
         </is>
       </c>
       <c r="E202" s="2" t="n"/>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>★칩스확정</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>"토하셨어요?"</t>
+        </is>
+      </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="n"/>
+          <t>오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>오심, 구토 없음</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B204" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>sensory motor circulation 확인함</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="n"/>
+          <t>dizziness 있음</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>dizziness 없음</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -5006,24 +5108,25 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>"예전보다 잘 안 보이세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>시력감퇴 있음</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>시력감퇴 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n"/>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -5033,24 +5136,25 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>"시야 일부가 가려지세요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>시야결손 있음</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>시야결손 없음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n"/>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -5060,24 +5164,24 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>복시 있음</t>
+          <t>감각이상 있음</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>복시 없음</t>
+          <t>감각이상 없음</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -5087,24 +5191,24 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>"눈이 충혈되었나요?"</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>결막충혈 있음</t>
+          <t>grasp power 약함</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>결막충혈 없음</t>
+          <t>grasp power 강함</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -5114,58 +5218,54 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>이물질 관찰됨</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
-        </is>
-      </c>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n"/>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>결막출혈 있음</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>결막출혈 없음</t>
-        </is>
-      </c>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C211" s="2" t="n"/>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>위세척에 대해 설명함</t>
         </is>
       </c>
       <c r="E211" s="2" t="n"/>
@@ -5173,7 +5273,7 @@
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -5184,7 +5284,7 @@
       <c r="C212" s="2" t="n"/>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>처방에 의해 해독제를 투여함</t>
         </is>
       </c>
       <c r="E212" s="2" t="n"/>
@@ -5192,7 +5292,7 @@
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>💊 약먹음</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -5203,7 +5303,7 @@
       <c r="C213" s="2" t="n"/>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E213" s="2" t="n"/>
@@ -5211,18 +5311,18 @@
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C214" s="2" t="n"/>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E214" s="2" t="n"/>
@@ -5230,18 +5330,22 @@
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B215" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>"부러진 곳(골절)이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>이물질 제거함</t>
+          <t>골절 있음</t>
         </is>
       </c>
       <c r="E215" s="2" t="n"/>
@@ -5249,164 +5353,172 @@
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>"다친 곳이 붓나요?"</t>
+        </is>
+      </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>안연고 점안 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="n"/>
+          <t>골절부위 edema 있음</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>골절부위 edema 없음</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>"저릿하거나 감각이 이상하세요?"</t>
+        </is>
+      </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="n"/>
+          <t>골절부위 tingling sense 있음</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>골절부위 tingling sense 없음</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B218" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
+        </is>
+      </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="n"/>
+          <t>찰과상 있음</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>찰과상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B219" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="n"/>
+          <t>출혈 있음</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>출혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>"피부가 가려우세요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n"/>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>가려움증 있음</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>가려움증 없음</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>"두드러기가 올라왔나요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n"/>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>urticaria 있음</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>urticaria 없음</t>
-        </is>
-      </c>
+          <t>골절부위 압박붕대 감아줌</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>"물집이 잡혔나요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n"/>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>bullae 있음</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>bullae 없음</t>
-        </is>
-      </c>
+          <t>골절부위 올려줌</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -5417,7 +5529,7 @@
       <c r="C223" s="2" t="n"/>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
       <c r="E223" s="2" t="n"/>
@@ -5425,7 +5537,7 @@
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -5436,7 +5548,7 @@
       <c r="C224" s="2" t="n"/>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>sensory motor circulation 확인함</t>
         </is>
       </c>
       <c r="E224" s="2" t="n"/>
@@ -5444,64 +5556,88 @@
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>"예전보다 잘 안 보이세요?"</t>
+        </is>
+      </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="n"/>
+          <t>시력감퇴 있음</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>시력감퇴 없음</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>"시야 일부가 가려지세요?"</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="n"/>
+          <t>시야결손 있음</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>시야결손 없음</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="n"/>
+          <t>복시 있음</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>복시 없음</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -5511,24 +5647,24 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"눈이 충혈되었나요?"</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
+          <t>결막충혈 있음</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>dizziness 없음</t>
+          <t>결막충혈 없음</t>
         </is>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -5538,25 +5674,20 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>이물질 관찰됨</t>
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="230" ht="18" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -5566,225 +5697,168 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="n"/>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>결막출혈 있음</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>결막출혈 없음</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n"/>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n"/>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n"/>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
-        </is>
-      </c>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n"/>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>사람에 대한 지남력 있음</t>
-        </is>
-      </c>
+          <t>안위변화</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n"/>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>섬망 있음</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
-        <is>
-          <t>섬망 없음</t>
-        </is>
-      </c>
+          <t>이물질 제거함</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n"/>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>환각 있음</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>환각 없음</t>
-        </is>
-      </c>
+          <t>안연고 점안 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>🩺 손떨림(flapping tremor)</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n"/>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>flapping tremor 있음</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>flapping tremor 없음</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n"/>
     </row>
     <row r="238" ht="36" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C238" s="2" t="n"/>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>안대 적용함</t>
         </is>
       </c>
       <c r="E238" s="2" t="n"/>
@@ -5792,7 +5866,7 @@
     <row r="239" ht="36" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -5803,7 +5877,7 @@
       <c r="C239" s="2" t="n"/>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
@@ -5811,75 +5885,99 @@
     <row r="240" ht="36" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B240" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="n"/>
+          <t>가려움증 있음</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>가려움증 없음</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="n"/>
+          <t>urticaria 있음</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>urticaria 없음</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="36" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B242" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>"물집이 잡혔나요?"</t>
+        </is>
+      </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="n"/>
+          <t>bullae 있음</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>bullae 없음</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B243" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C243" s="2" t="n"/>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="E243" s="2" t="n"/>
@@ -5887,7 +5985,7 @@
     <row r="244" ht="36" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>🧴 피부</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -5898,7 +5996,7 @@
       <c r="C244" s="2" t="n"/>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="E244" s="2" t="n"/>
@@ -5906,49 +6004,37 @@
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B245" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n"/>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>자해나 자살시도를 부인함</t>
-        </is>
-      </c>
+          <t>소양증 감소 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n"/>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="E246" s="2" t="n"/>
@@ -5956,22 +6042,18 @@
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B247" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B247" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n"/>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="E247" s="2" t="n"/>
@@ -5979,7 +6061,7 @@
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
+          <t>🌀 의식이상</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -5989,24 +6071,24 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>🩺 공격적 행동(관찰)</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>공격적 행동함</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>타인에 대한 공격적 행동을 보이지 않음</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
+          <t>🌀 의식이상</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -6016,187 +6098,253 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>공황상태 있음</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>공황상태 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n"/>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B250" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E250" s="2" t="n"/>
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B252" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B254" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+        </is>
+      </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>진정시킴</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="n"/>
+          <t>사람에 대한 지남력 없음</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>사람에 대한 지남력 있음</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B255" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="n"/>
+          <t>섬망 있음</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>섬망 없음</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B256" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>"없는 것이 보이거나 들리세요?"</t>
+        </is>
+      </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="n"/>
+          <t>환각 있음</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>환각 없음</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B257" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>🩺 손떨림(flapping tremor)</t>
+        </is>
+      </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="n"/>
+          <t>flapping tremor 있음</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>flapping tremor 없음</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B258" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C258" s="2" t="n"/>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>경청해줌</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="E258" s="2" t="n"/>
@@ -6204,172 +6352,121 @@
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n"/>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n"/>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n"/>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>국부 마비 있음</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>국부 마비 없음</t>
-        </is>
-      </c>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n"/>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>알코올 섭취 양상을 확인함</t>
         </is>
       </c>
       <c r="E262" s="2" t="n"/>
-      <c r="F262" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 상태</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B263" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n"/>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
+          <t>금단 증상을 설명함</t>
         </is>
       </c>
       <c r="E263" s="2" t="n"/>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n"/>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E264" s="2" t="n"/>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -6379,24 +6476,24 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
+          <t>구체적 자살계획을 언급함</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능함</t>
+          <t>자해나 자살시도를 부인함</t>
         </is>
       </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -6406,35 +6503,35 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>seizure 있음</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>seizure 없음</t>
-        </is>
-      </c>
+          <t>자살을 시도함</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살 충동 있음</t>
         </is>
       </c>
       <c r="E267" s="2" t="n"/>
@@ -6442,45 +6539,61 @@
     <row r="268" ht="18" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B268" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>🩺 공격적 행동(관찰)</t>
+        </is>
+      </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="n"/>
+          <t>공격적 행동함</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>타인에 대한 공격적 행동을 보이지 않음</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B269" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+        </is>
+      </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="n"/>
+          <t>공황상태 있음</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>공황상태 없음</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
@@ -6491,7 +6604,7 @@
       <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="E270" s="2" t="n"/>
@@ -6499,7 +6612,7 @@
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -6510,7 +6623,7 @@
       <c r="C271" s="2" t="n"/>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E271" s="2" t="n"/>
@@ -6518,7 +6631,7 @@
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -6529,7 +6642,7 @@
       <c r="C272" s="2" t="n"/>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="E272" s="2" t="n"/>
@@ -6537,78 +6650,56 @@
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n"/>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>혈압 SBP/DBP (mmHg 입력)</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
       <c r="E273" s="2" t="n"/>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n"/>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
-      <c r="F274" s="5" t="n"/>
+          <t>진정시킴</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="n"/>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>혈압 상승됨</t>
+          <t>억제대 적용 중임</t>
         </is>
       </c>
       <c r="E275" s="2" t="n"/>
@@ -6616,22 +6707,18 @@
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n"/>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
+          <t>불안</t>
         </is>
       </c>
       <c r="E276" s="2" t="n"/>
@@ -6639,49 +6726,37 @@
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n"/>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>고혈압으로 인한 증상 있음</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>고혈압으로 인한 증상 없음</t>
-        </is>
-      </c>
+          <t>불안을 감소시켜 줌</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n"/>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 있음</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="E278" s="2" t="n"/>
@@ -6689,255 +6764,294 @@
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="36" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B280" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
+        </is>
+      </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B281" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
+        </is>
+      </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Non Invasive BP monitor 시작함</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="n"/>
+          <t>국부 마비 있음</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>국부 마비 없음</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B282" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>혈압관리 방법에 대해 교육함</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
         </is>
       </c>
       <c r="E282" s="2" t="n"/>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B283" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 상태</t>
+        </is>
+      </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
         </is>
       </c>
       <c r="E283" s="2" t="n"/>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B284" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E284" s="2" t="n"/>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B285" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B286" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="n"/>
+          <t>seizure 있음</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>seizure 없음</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하세요?"</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n"/>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 없음</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>"가슴이 답답하거나 불편하세요?"</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n"/>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>흉부 불편감 없음</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>"식은땀이 나세요?"</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B289" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n"/>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>식은땀 있음</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>식은땀 없음</t>
-        </is>
-      </c>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>🩺 맥박 불규칙(촉지)</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n"/>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E290" s="2" t="n"/>
@@ -6945,45 +7059,37 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B291" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>심전도 리듬 상 부정맥 여부</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n"/>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>부정맥 있음</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>부정맥 없음</t>
-        </is>
-      </c>
+          <t>seizure 양상 확인함</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C292" s="2" t="n"/>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E292" s="2" t="n"/>
@@ -6991,56 +7097,78 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B293" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+        </is>
+      </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
+          <t>혈압 SBP/DBP (mmHg 입력)</t>
         </is>
       </c>
       <c r="E293" s="2" t="n"/>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="n"/>
+          <t>dizziness 있음</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F294" s="5" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B295" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C295" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
+          <t>혈압 상승됨</t>
         </is>
       </c>
       <c r="E295" s="2" t="n"/>
@@ -7048,18 +7176,22 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B296" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
+        </is>
+      </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>부정맥이 있는지 확인함</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="E296" s="2" t="n"/>
@@ -7067,7 +7199,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -7075,18 +7207,26 @@
           <t>사정</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n"/>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
+        </is>
+      </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="n"/>
+          <t>고혈압으로 인한 증상 있음</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>고혈압으로 인한 증상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -7094,10 +7234,14 @@
           <t>사정</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n"/>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Coma Scale : (E+V+M)</t>
+          <t>체위성 저혈압 있음</t>
         </is>
       </c>
       <c r="E298" s="2" t="n"/>
@@ -7105,18 +7249,18 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C299" s="2" t="n"/>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>의식수준 저하됨</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="E299" s="2" t="n"/>
@@ -7124,18 +7268,18 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C300" s="2" t="n"/>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="E300" s="2" t="n"/>
@@ -7143,18 +7287,18 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C301" s="2" t="n"/>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="E301" s="2" t="n"/>
@@ -7162,18 +7306,18 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B302" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C302" s="2" t="n"/>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>혈압관리 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E302" s="2" t="n"/>
@@ -7181,18 +7325,18 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B303" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C303" s="2" t="n"/>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>낙상방지 교육함</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="E303" s="2" t="n"/>
@@ -7200,7 +7344,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -7211,7 +7355,7 @@
       <c r="C304" s="2" t="n"/>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>침대 난간을 올려줌</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="E304" s="2" t="n"/>
@@ -7219,7 +7363,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -7230,7 +7374,7 @@
       <c r="C305" s="2" t="n"/>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>보호자와 같이 있게 함</t>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E305" s="2" t="n"/>
@@ -7238,7 +7382,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -7248,6 +7392,422 @@
       </c>
       <c r="C306" s="2" t="n"/>
       <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하세요?"</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>호흡곤란 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>"가슴이 답답하거나 불편하세요?"</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>흉부 불편감 있음</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>흉부 불편감 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>"식은땀이 나세요?"</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>식은땀 있음</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>식은땀 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>🩺 맥박 불규칙(촉지)</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>불규칙 맥박 촉지됨</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>심전도 리듬 상 부정맥 여부</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>부정맥 있음</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>부정맥 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="n"/>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B313" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n"/>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>흉부 통증이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B314" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n"/>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>EKG monitor 시작함</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B315" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n"/>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>심전도 변화를 확인함</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="n"/>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>부정맥이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="n"/>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>의식 명료함</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="n"/>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow Coma Scale : (E+V+M)</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n"/>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>의식수준 저하됨</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n"/>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n"/>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n"/>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B323" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="n"/>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>낙상방지 교육함</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B324" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="n"/>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>침대 난간을 올려줌</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B325" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="n"/>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>보호자와 같이 있게 함</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B326" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="n"/>
+      <c r="D326" s="2" t="inlineStr">
         <is>
           <t>보호자 동반하라고 설명함</t>
         </is>

--- a/nursing/통합간호기록_사정진단평가_260626.xlsx
+++ b/nursing/통합간호기록_사정진단평가_260626.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F318"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>"손발이 저리거나 근육이 경련되세요?"</t>
+          <t>🩺 tetany 증상 (손발·입 주위 저림, 근육 경련, Chvostek·Trousseau 징후, 반궁긴장, 광과민, 발작 등 신경근 과흥분)</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -2921,7 +2921,16 @@
           <t>tetany 증상 있음</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>tetany 증상 없음(Chvosteck's sign, Trousseau's sign, 반궁긴장, 저린감, perioral numbness, photohypersensitivity, seizure, cramp)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -3104,12 +3113,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>🩺 Chvostek 징후 — 귀 앞쪽 뺨(안면신경)을 손가락으로 톡톡 두드렸을 때 입꼬리·얼굴이 씰룩이면 양성</t>
+          <t>🩺 심전도 QT 간격 연장 (저칼슘)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Chvostek sign 있음</t>
+          <t>QT 간격 연장되어 있음</t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
@@ -3132,12 +3141,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>🩺 Trousseau 징후 — 혈압계 커프를 수축기압보다 20mmHg 높여 3분 유지했을 때 손목·손가락이 굽고 뻣뻣해지면 양성</t>
+          <t>🩺 부정맥 (불규칙한 맥박)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Trousseau's sign 있음</t>
+          <t>부정맥 있음</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
@@ -3160,20 +3169,15 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>🩺 수족 경련(carpopedal spasm) — 손목·발목이 안쪽으로 굽으며 뻣뻣하게 경련함</t>
+          <t>🩺 혈중 나트륨(Na) 높음</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>carpopedal spasm 있음</t>
+          <t>혈중 sodium 수치 정상 이상임</t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>칼슘</t>
-        </is>
-      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -3188,20 +3192,15 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>"입술이나 입 주위가 저리거나 얼얼하세요?"</t>
+          <t>🩺 혈중 나트륨(Na) 낮음</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Perioral numbness</t>
+          <t>혈중 sodium 수치 정상 이하임</t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>칼슘</t>
-        </is>
-      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -3216,18 +3215,18 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>"손발이 저리세요?"</t>
+          <t>"갈증이 많이 나세요?"</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>이상감각 있음</t>
+          <t>갈증 있음</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>칼슘</t>
+          <t>나트륨</t>
         </is>
       </c>
     </row>
@@ -3244,18 +3243,18 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>🩺 심전도 QT 간격 연장 (저칼슘)</t>
+          <t>"메스껍거나 토하세요?"</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>QT 간격 연장되어 있음</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>칼슘</t>
+          <t>나트륨</t>
         </is>
       </c>
     </row>
@@ -3272,18 +3271,18 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>🩺 부정맥 (불규칙한 맥박)</t>
+          <t>🩺 의식수준 저하 (처지고 반응이 둔함)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>부정맥 있음</t>
+          <t>의식수준 저하됨</t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>칼슘</t>
+          <t>나트륨</t>
         </is>
       </c>
     </row>
@@ -3300,15 +3299,20 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈중 나트륨(Na) 높음</t>
+          <t>🩺 경련·발작 보임</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이상임</t>
+          <t>경련 있음</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -3316,19 +3320,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈중 나트륨(Na) 낮음</t>
-        </is>
-      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이하임</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
@@ -3339,27 +3339,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>"갈증이 많이 나세요?"</t>
-        </is>
-      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>갈증 있음</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -3367,27 +3358,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>🩺 소변량 감소·핍뇨</t>
-        </is>
-      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>처방에 의해 인슐린 투여함</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -3395,27 +3377,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>🩺 의식수준 저하 (처지고 반응이 둔함)</t>
-        </is>
-      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>의식수준 저하됨</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -3423,27 +3396,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>🩺 경련·발작 보임</t>
-        </is>
-      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>경련 있음</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -3451,27 +3415,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>"머리가 아프세요?"</t>
-        </is>
-      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>두통 있음</t>
+          <t>처방에 의해 D50W 을 투여함</t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -3479,27 +3434,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>"메스껍거나 토하세요?"</t>
-        </is>
-      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
+          <t>고칼륨혈증</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -3507,27 +3453,18 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>"기운이 없고 축 처지세요?"</t>
-        </is>
-      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>무기력 호소함</t>
+          <t>hyperkalemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -3535,15 +3472,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -3562,7 +3499,7 @@
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>고칼륨식이 섭취 제한하도록 교육함</t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
@@ -3581,7 +3518,7 @@
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 인슐린 투여함</t>
+          <t>혈중 potassium  검사결과 확인함</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -3592,15 +3529,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -3611,15 +3548,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -3638,7 +3575,7 @@
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 D50W 을 투여함</t>
+          <t>hypokalemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -3649,15 +3586,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>고칼륨혈증</t>
+          <t>혈중 potassium  검사결과 확인함</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -3676,7 +3613,7 @@
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>hyperkalemia 증상이 있는지 확인함</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -3695,7 +3632,7 @@
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>고칼륨식이 섭취 격려함</t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -3706,15 +3643,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 제한하도록 교육함</t>
+          <t>고칼슘혈증</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -3733,7 +3670,7 @@
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>혈중 potassium  검사결과 확인함</t>
+          <t>hypercalcemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -3752,7 +3689,7 @@
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
+          <t>혈중 calcium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
@@ -3763,15 +3700,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>칼슘 섭취를 제한하도록 함</t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
@@ -3782,15 +3719,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>hypokalemia 증상이 있는지 확인함</t>
+          <t>저칼슘혈증</t>
         </is>
       </c>
       <c r="E145" s="2" t="n"/>
@@ -3809,7 +3746,7 @@
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>혈중 potassium  검사결과 확인함</t>
+          <t>hypocalcemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E146" s="2" t="n"/>
@@ -3828,7 +3765,7 @@
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>혈중 calcium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E147" s="2" t="n"/>
@@ -3847,7 +3784,7 @@
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 격려함</t>
+          <t>처방에 의해 Calcium gluconate 를 투여함</t>
         </is>
       </c>
       <c r="E148" s="2" t="n"/>
@@ -3866,7 +3803,7 @@
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>고칼슘혈증</t>
+          <t>고나트륨혈증</t>
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
@@ -3885,7 +3822,7 @@
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>hypercalcemia 증상이 있는지 확인함</t>
+          <t>hypernatremia의 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
@@ -3904,7 +3841,7 @@
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>혈중 calcium 검사결과 확인함</t>
+          <t>혈중 sodium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
@@ -3915,15 +3852,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>칼슘 섭취를 제한하도록 함</t>
+          <t>저나트륨혈증</t>
         </is>
       </c>
       <c r="E152" s="2" t="n"/>
@@ -3934,15 +3871,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>저칼슘혈증</t>
+          <t>hyponatremia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E153" s="2" t="n"/>
@@ -3961,7 +3898,7 @@
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>hypocalcemia 증상이 있는지 확인함</t>
+          <t>혈중 sodium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E154" s="2" t="n"/>
@@ -3980,7 +3917,7 @@
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>혈중 calcium 검사결과 확인함</t>
+          <t>sodium 섭취를 늘리도록 교육함</t>
         </is>
       </c>
       <c r="E155" s="2" t="n"/>
@@ -3999,7 +3936,7 @@
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Calcium gluconate 를 투여함</t>
+          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
         </is>
       </c>
       <c r="E156" s="2" t="n"/>
@@ -4007,94 +3944,130 @@
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>"소변보기 힘드세요?"</t>
+        </is>
+      </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>고나트륨혈증</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="n"/>
+          <t>배뇨곤란 있음</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>배뇨곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>"소변이 막힌 느낌이세요?"</t>
+        </is>
+      </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>hypernatremia의 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="n"/>
+          <t>요정체 있음</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>요정체 없음</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="n"/>
+          <t>잔뇨감 있음</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>잔뇨감 없음</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>"소변에 피가 보이나요?"</t>
+        </is>
+      </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>저나트륨혈증</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="n"/>
+          <t>혈뇨 있음</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>혈뇨 없음</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n"/>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>🩺 소변량 감소</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>hyponatremia 증상이 있는지 확인함</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="E161" s="2" t="n"/>
@@ -4102,18 +4075,18 @@
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
-        </is>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>배뇨장애</t>
         </is>
       </c>
       <c r="E162" s="2" t="n"/>
@@ -4121,7 +4094,7 @@
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
@@ -4132,7 +4105,7 @@
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>sodium 섭취를 늘리도록 교육함</t>
+          <t>요정체가 있는지 확인함</t>
         </is>
       </c>
       <c r="E163" s="2" t="n"/>
@@ -4140,7 +4113,7 @@
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>🍬 혈당·전해질</t>
+          <t>🚽 소변</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
@@ -4151,7 +4124,7 @@
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
+          <t>단순도뇨 시행함</t>
         </is>
       </c>
       <c r="E164" s="2" t="n"/>
@@ -4162,31 +4135,23 @@
           <t>🚽 소변</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>"소변보기 힘드세요?"</t>
-        </is>
-      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>배뇨곤란 있음</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>배뇨곤란 없음</t>
-        </is>
-      </c>
+          <t>혈뇨가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -4196,24 +4161,24 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>"소변이 막힌 느낌이세요?"</t>
+          <t>"귀에서 분비물이 나오세요?"</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>요정체 있음</t>
+          <t>귀분비물 있음</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>요정체 없음</t>
+          <t>귀분비물 없음</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -4223,24 +4188,24 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+          <t>"귀울림(이명)이 있으세요?"</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>잔뇨감 있음</t>
+          <t>이명 있음</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>잔뇨감 없음</t>
+          <t>이명 없음</t>
         </is>
       </c>
     </row>
     <row r="168" ht="36" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -4250,24 +4215,20 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>"소변에 피가 보이나요?"</t>
+          <t>"잘 안 들리세요?"</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>혈뇨 있음</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>혈뇨 없음</t>
-        </is>
-      </c>
+          <t>청력 이상 있음</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -4277,69 +4238,89 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>🩺 소변량 감소</t>
+          <t>"코가 막히세요?"</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="n"/>
+          <t>코막힘 있음</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>코막힘 없음</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>"콧물이 나세요?"</t>
+        </is>
+      </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="n"/>
+          <t>콧물 있음</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>콧물 없음</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>"삼키기 힘드세요?"</t>
+        </is>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="n"/>
+          <t>연하곤란 있음</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>연하곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>단순도뇨 시행함</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="E172" s="2" t="n"/>
@@ -4347,7 +4328,7 @@
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
+          <t>👂 귀·코·목</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -4358,7 +4339,7 @@
       <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E173" s="2" t="n"/>
@@ -4369,26 +4350,18 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>"귀에서 분비물이 나오세요?"</t>
-        </is>
-      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>귀분비물 있음</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>귀분비물 없음</t>
-        </is>
-      </c>
+          <t>청력장애가 있는지 사정함</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -4396,31 +4369,23 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>"귀울림(이명)이 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n"/>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>이명 있음</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>이명 없음</t>
-        </is>
-      </c>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -4430,20 +4395,24 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>"잘 안 들리세요?"</t>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>청력 이상 있음</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="n"/>
+          <t>오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>오심, 구토 없음</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -4453,24 +4422,24 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>"코가 막히세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>코막힘 있음</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>코막힘 없음</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -4480,24 +4449,25 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>"콧물이 나세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>콧물 있음</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>콧물 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
+          <t>💫 어지러워</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -4507,95 +4477,128 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>"삼키기 힘드세요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>연하곤란 있음</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>연하곤란 없음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>청력장애가 있는지 사정함</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="n"/>
+          <t>vertigo 있음</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>vertigo 없음</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n"/>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+        </is>
+      </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="n"/>
+          <t>syncope 있음</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>syncope 없음</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -4610,17 +4613,17 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
+          <t>obey command 가능하지 않음</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음</t>
+          <t>obey command 가능함</t>
         </is>
       </c>
     </row>
@@ -4630,26 +4633,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n"/>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -4657,27 +4652,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n"/>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E186" s="2" t="n"/>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -4685,27 +4671,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n"/>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E187" s="2" t="n"/>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -4713,26 +4690,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n"/>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -4740,26 +4709,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
-        </is>
-      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n"/>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -4767,26 +4728,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>vertigo 있음</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>vertigo 없음</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -4794,26 +4747,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>syncope 있음</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>syncope 없음</t>
-        </is>
-      </c>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -4821,26 +4766,18 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
-        </is>
-      </c>
+          <t>조직관류 증진 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -4848,15 +4785,15 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B193" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E193" s="2" t="n"/>
@@ -4864,154 +4801,221 @@
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B194" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>음독 함 ★</t>
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>★칩스확정</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>"토하셨어요?"</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="n"/>
+          <t>오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>오심, 구토 없음</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B196" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="n"/>
+          <t>dizziness 있음</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>dizziness 없음</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
         </is>
       </c>
       <c r="E197" s="2" t="n"/>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B198" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E198" s="2" t="n"/>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B200" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>조직관류 증진 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B201" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="n"/>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="18" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -5019,27 +5023,18 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
-        </is>
-      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n"/>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>음독 함 ★</t>
+          <t>중독위험</t>
         </is>
       </c>
       <c r="E202" s="2" t="n"/>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>★칩스확정</t>
-        </is>
-      </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -5047,26 +5042,18 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>"토하셨어요?"</t>
-        </is>
-      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n"/>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>오심, 구토 없음</t>
-        </is>
-      </c>
+          <t>위세척에 대해 설명함</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -5074,26 +5061,18 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n"/>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
+          <t>처방에 의해 해독제를 투여함</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -5101,27 +5080,18 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n"/>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E205" s="2" t="n"/>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -5129,32 +5099,23 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n"/>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E206" s="2" t="n"/>
-      <c r="F206" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -5164,24 +5125,20 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"부러진 곳(골절)이 있으세요?"</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>골절 있음</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -5191,24 +5148,24 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"다친 곳이 붓나요?"</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
+          <t>골절부위 edema 있음</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함</t>
+          <t>골절부위 edema 없음</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -5218,73 +5175,89 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+          <t>"저릿하거나 감각이 이상하세요?"</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
+          <t>골절부위 tingling sense 있음</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능함</t>
+          <t>골절부위 tingling sense 없음</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
+        </is>
+      </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>중독위험</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="n"/>
+          <t>찰과상 있음</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>찰과상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B211" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="n"/>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>위세척에 대해 설명함</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="n"/>
+          <t>출혈 있음</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>출혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B212" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C212" s="2" t="n"/>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 해독제를 투여함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E212" s="2" t="n"/>
@@ -5292,7 +5265,7 @@
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
@@ -5303,7 +5276,7 @@
       <c r="C213" s="2" t="n"/>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>골절부위 압박붕대 감아줌</t>
         </is>
       </c>
       <c r="E213" s="2" t="n"/>
@@ -5311,7 +5284,7 @@
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
+          <t>🤕 다쳤어</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -5322,7 +5295,7 @@
       <c r="C214" s="2" t="n"/>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>골절부위 올려줌</t>
         </is>
       </c>
       <c r="E214" s="2" t="n"/>
@@ -5333,19 +5306,15 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>"부러진 곳(골절)이 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n"/>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>골절 있음</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
       <c r="E215" s="2" t="n"/>
@@ -5356,31 +5325,23 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>"다친 곳이 붓나요?"</t>
-        </is>
-      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n"/>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>골절부위 edema 있음</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>골절부위 edema 없음</t>
-        </is>
-      </c>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -5390,24 +5351,24 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>"저릿하거나 감각이 이상하세요?"</t>
+          <t>"예전보다 잘 안 보이세요?"</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>골절부위 tingling sense 있음</t>
+          <t>시력감퇴 있음</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>골절부위 tingling sense 없음</t>
+          <t>시력감퇴 없음</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -5417,24 +5378,24 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
+          <t>"시야 일부가 가려지세요?"</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>찰과상 있음</t>
+          <t>시야결손 있음</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>찰과상 없음</t>
+          <t>시야결손 없음</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -5444,54 +5405,66 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>"피가 나나요?"</t>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>출혈 있음</t>
+          <t>복시 있음</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>출혈 없음</t>
+          <t>복시 없음</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B220" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>"눈이 충혈되었나요?"</t>
+        </is>
+      </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="n"/>
+          <t>결막충혈 있음</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>결막충혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B221" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
+        </is>
+      </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>골절부위 압박붕대 감아줌</t>
+          <t>이물질 관찰됨</t>
         </is>
       </c>
       <c r="E221" s="2" t="n"/>
@@ -5499,26 +5472,34 @@
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B222" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="n"/>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
+        </is>
+      </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>골절부위 올려줌</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="n"/>
+          <t>결막출혈 있음</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>결막출혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
@@ -5529,7 +5510,7 @@
       <c r="C223" s="2" t="n"/>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
       <c r="E223" s="2" t="n"/>
@@ -5537,7 +5518,7 @@
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
+          <t>👁️ 눈</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -5548,7 +5529,7 @@
       <c r="C224" s="2" t="n"/>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>sensory motor circulation 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E224" s="2" t="n"/>
@@ -5559,26 +5540,18 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>"예전보다 잘 안 보이세요?"</t>
-        </is>
-      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n"/>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>시력감퇴 있음</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>시력감퇴 없음</t>
-        </is>
-      </c>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -5586,26 +5559,18 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>"시야 일부가 가려지세요?"</t>
-        </is>
-      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n"/>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>시야결손 있음</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>시야결손 없음</t>
-        </is>
-      </c>
+          <t>안위변화</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n"/>
     </row>
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -5613,26 +5578,18 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
-        </is>
-      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n"/>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>복시 있음</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>복시 없음</t>
-        </is>
-      </c>
+          <t>이물질 제거함</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -5640,26 +5597,18 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>"눈이 충혈되었나요?"</t>
-        </is>
-      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n"/>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>결막충혈 있음</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>결막충혈 없음</t>
-        </is>
-      </c>
+          <t>안연고 점안 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
@@ -5667,19 +5616,15 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
-        </is>
-      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n"/>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>이물질 관찰됨</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
@@ -5690,26 +5635,18 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
-        </is>
-      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n"/>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>결막출혈 있음</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>결막출혈 없음</t>
-        </is>
-      </c>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
@@ -5717,15 +5654,15 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C231" s="2" t="n"/>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E231" s="2" t="n"/>
@@ -5733,75 +5670,99 @@
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B232" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="n"/>
+          <t>가려움증 있음</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>가려움증 없음</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B233" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="n"/>
+          <t>urticaria 있음</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>urticaria 없음</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B234" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="n"/>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>"물집이 잡혔나요?"</t>
+        </is>
+      </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>안위변화</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="n"/>
+          <t>bullae 있음</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>bullae 없음</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B235" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C235" s="2" t="n"/>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>이물질 제거함</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="E235" s="2" t="n"/>
@@ -5809,7 +5770,7 @@
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>🧴 피부</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -5820,7 +5781,7 @@
       <c r="C236" s="2" t="n"/>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>안연고 점안 방법에 대해 교육함</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="E236" s="2" t="n"/>
@@ -5828,18 +5789,18 @@
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C237" s="2" t="n"/>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E237" s="2" t="n"/>
@@ -5847,18 +5808,18 @@
     <row r="238" ht="36" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C238" s="2" t="n"/>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="E238" s="2" t="n"/>
@@ -5866,7 +5827,7 @@
     <row r="239" ht="36" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
+          <t>🧴 피부</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
@@ -5877,7 +5838,7 @@
       <c r="C239" s="2" t="n"/>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
@@ -5885,7 +5846,7 @@
     <row r="240" ht="36" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
+          <t>🌀 의식이상</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -5895,24 +5856,24 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>"피부가 가려우세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>가려움증 있음</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>가려움증 없음</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
+          <t>🌀 의식이상</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -5922,24 +5883,25 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>"두드러기가 올라왔나요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>urticaria 있음</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>urticaria 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n"/>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="242" ht="36" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
+          <t>🌀 의식이상</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -5949,114 +5911,155 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>"물집이 잡혔나요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>bullae 있음</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>bullae 없음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n"/>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="36" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B244" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="18" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B245" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="18" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+        </is>
+      </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="n"/>
+          <t>사람에 대한 지남력 없음</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>사람에 대한 지남력 있음</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="18" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B247" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="n"/>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+        </is>
+      </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="n"/>
+          <t>섬망 있음</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>섬망 없음</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -6071,17 +6074,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"없는 것이 보이거나 들리세요?"</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
+          <t>환각 있음</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>dizziness 없음</t>
+          <t>환각 없음</t>
         </is>
       </c>
     </row>
@@ -6098,18 +6101,17 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>🩺 손떨림(flapping tremor)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="n"/>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>flapping tremor 있음</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>flapping tremor 없음</t>
         </is>
       </c>
     </row>
@@ -6119,27 +6121,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n"/>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="E250" s="2" t="n"/>
-      <c r="F250" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
@@ -6147,26 +6140,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+      <c r="B251" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n"/>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -6174,26 +6159,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
-        </is>
-      </c>
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n"/>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -6201,26 +6178,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n"/>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
-        </is>
-      </c>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -6228,26 +6197,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
-        </is>
-      </c>
+      <c r="B254" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n"/>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>사람에 대한 지남력 있음</t>
-        </is>
-      </c>
+          <t>알코올 섭취 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
@@ -6255,26 +6216,18 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
-        </is>
-      </c>
+      <c r="B255" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n"/>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>섬망 있음</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>섬망 없음</t>
-        </is>
-      </c>
+          <t>금단 증상을 설명함</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -6282,31 +6235,23 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
-        </is>
-      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n"/>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>환각 있음</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>환각 없음</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -6316,35 +6261,39 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>🩺 손떨림(flapping tremor)</t>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>flapping tremor 있음</t>
+          <t>구체적 자살계획을 언급함</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>flapping tremor 없음</t>
+          <t>자해나 자살시도를 부인함</t>
         </is>
       </c>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살을 시도함</t>
         </is>
       </c>
       <c r="E258" s="2" t="n"/>
@@ -6352,18 +6301,22 @@
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B259" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>자살 충동 있음</t>
         </is>
       </c>
       <c r="E259" s="2" t="n"/>
@@ -6371,56 +6324,72 @@
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B260" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>🩺 공격적 행동(관찰)</t>
+        </is>
+      </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="n"/>
+          <t>공격적 행동함</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>타인에 대한 공격적 행동을 보이지 않음</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="n"/>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+        </is>
+      </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="n"/>
+          <t>공황상태 있음</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>공황상태 없음</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B262" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C262" s="2" t="n"/>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="E262" s="2" t="n"/>
@@ -6428,7 +6397,7 @@
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -6439,7 +6408,7 @@
       <c r="C263" s="2" t="n"/>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E263" s="2" t="n"/>
@@ -6447,7 +6416,7 @@
     <row r="264" ht="18" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
+          <t>😰 불안·자해</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -6458,7 +6427,7 @@
       <c r="C264" s="2" t="n"/>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="E264" s="2" t="n"/>
@@ -6469,26 +6438,18 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n"/>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>자해나 자살시도를 부인함</t>
-        </is>
-      </c>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -6496,19 +6457,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n"/>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>진정시킴</t>
         </is>
       </c>
       <c r="E266" s="2" t="n"/>
@@ -6519,19 +6476,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="n"/>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
+          <t>억제대 적용 중임</t>
         </is>
       </c>
       <c r="E267" s="2" t="n"/>
@@ -6542,26 +6495,18 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>🩺 공격적 행동(관찰)</t>
-        </is>
-      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n"/>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>공격적 행동함</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>타인에 대한 공격적 행동을 보이지 않음</t>
-        </is>
-      </c>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
@@ -6569,26 +6514,18 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
-        </is>
-      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n"/>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>공황상태 있음</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>공황상태 없음</t>
-        </is>
-      </c>
+          <t>불안을 감소시켜 줌</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -6596,15 +6533,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="E270" s="2" t="n"/>
@@ -6612,154 +6549,221 @@
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B271" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B272" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
+        </is>
+      </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
+        </is>
+      </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="n"/>
+          <t>국부 마비 있음</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>국부 마비 없음</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B274" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>진정시킴</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
         </is>
       </c>
       <c r="E274" s="2" t="n"/>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B275" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 상태</t>
+        </is>
+      </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
+          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
         </is>
       </c>
       <c r="E275" s="2" t="n"/>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="18" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B276" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E276" s="2" t="n"/>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="18" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B277" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="18" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B278" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="n"/>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>경청해줌</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="n"/>
+          <t>seizure 있음</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>seizure 없음</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="18" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
@@ -6767,26 +6771,18 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n"/>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n"/>
     </row>
     <row r="280" ht="36" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -6794,26 +6790,18 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
-        </is>
-      </c>
+      <c r="B280" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n"/>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -6821,26 +6809,18 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
-        </is>
-      </c>
+      <c r="B281" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n"/>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>국부 마비 있음</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>국부 마비 없음</t>
-        </is>
-      </c>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -6848,27 +6828,18 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n"/>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E282" s="2" t="n"/>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -6876,27 +6847,18 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 상태</t>
-        </is>
-      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n"/>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="E283" s="2" t="n"/>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="284" ht="18" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -6904,32 +6866,23 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B284" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+      <c r="B284" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n"/>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E284" s="2" t="n"/>
-      <c r="F284" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -6939,24 +6892,25 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
+          <t>혈압 SBP/DBP (mmHg 입력)</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n"/>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -6966,35 +6920,40 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>seizure 있음</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>seizure 없음</t>
-        </is>
-      </c>
+          <t>dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B287" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>혈압 상승됨</t>
         </is>
       </c>
       <c r="E287" s="2" t="n"/>
@@ -7002,18 +6961,22 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B288" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
+        </is>
+      </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="E288" s="2" t="n"/>
@@ -7021,37 +6984,49 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B289" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
+        </is>
+      </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="n"/>
+          <t>고혈압으로 인한 증상 있음</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>고혈압으로 인한 증상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="n"/>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>체위성 저혈압 있음</t>
         </is>
       </c>
       <c r="E290" s="2" t="n"/>
@@ -7059,18 +7034,18 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B291" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C291" s="2" t="n"/>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="E291" s="2" t="n"/>
@@ -7078,7 +7053,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
+          <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -7089,7 +7064,7 @@
       <c r="C292" s="2" t="n"/>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="E292" s="2" t="n"/>
@@ -7100,27 +7075,18 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B293" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
-        </is>
-      </c>
+      <c r="B293" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n"/>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>혈압 SBP/DBP (mmHg 입력)</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="E293" s="2" t="n"/>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -7128,27 +7094,18 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B294" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+      <c r="B294" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n"/>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
-      <c r="F294" s="5" t="n"/>
+          <t>혈압관리 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -7156,19 +7113,15 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B295" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
-        </is>
-      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n"/>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>혈압 상승됨</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="E295" s="2" t="n"/>
@@ -7179,19 +7132,15 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B296" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
-        </is>
-      </c>
+      <c r="B296" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n"/>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="E296" s="2" t="n"/>
@@ -7202,26 +7151,18 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B297" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
-        </is>
-      </c>
+      <c r="B297" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n"/>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>고혈압으로 인한 증상 있음</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>고혈압으로 인한 증상 없음</t>
-        </is>
-      </c>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -7229,19 +7170,15 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B298" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
-        </is>
-      </c>
+      <c r="B298" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n"/>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 있음</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E298" s="2" t="n"/>
@@ -7249,75 +7186,103 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B299" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="n"/>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하세요?"</t>
+        </is>
+      </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="n"/>
+          <t>호흡곤란 있음</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>호흡곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B300" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="n"/>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>"가슴이 답답하거나 불편하세요?"</t>
+        </is>
+      </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="n"/>
+          <t>흉부 불편감 있음</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>흉부 불편감 없음</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B301" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="n"/>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>"식은땀이 나세요?"</t>
+        </is>
+      </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Non Invasive BP monitor 시작함</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="n"/>
+          <t>식은땀 있음</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>식은땀 없음</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B302" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="n"/>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>🩺 맥박 불규칙(촉지)</t>
+        </is>
+      </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>혈압관리 방법에 대해 교육함</t>
+          <t>불규칙 맥박 촉지됨</t>
         </is>
       </c>
       <c r="E302" s="2" t="n"/>
@@ -7325,37 +7290,45 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B303" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="n"/>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>심전도 리듬 상 부정맥 여부</t>
+        </is>
+      </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="n"/>
+          <t>부정맥 있음</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>부정맥 없음</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B304" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C304" s="2" t="n"/>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
       <c r="E304" s="2" t="n"/>
@@ -7363,7 +7336,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
+          <t>❤️ 심장</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -7374,7 +7347,7 @@
       <c r="C305" s="2" t="n"/>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
+          <t>흉부 통증이 있는지 확인함</t>
         </is>
       </c>
       <c r="E305" s="2" t="n"/>
@@ -7382,7 +7355,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
+          <t>❤️ 심장</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -7393,7 +7366,7 @@
       <c r="C306" s="2" t="n"/>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E306" s="2" t="n"/>
@@ -7404,26 +7377,18 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B307" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하세요?"</t>
-        </is>
-      </c>
+      <c r="B307" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="n"/>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 없음</t>
-        </is>
-      </c>
+          <t>심전도 변화를 확인함</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -7431,31 +7396,23 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>"가슴이 답답하거나 불편하세요?"</t>
-        </is>
-      </c>
+      <c r="B308" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="n"/>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음</t>
-        </is>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>흉부 불편감 없음</t>
-        </is>
-      </c>
+          <t>부정맥이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
+          <t>의식/낙상 (항상)</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -7463,26 +7420,18 @@
           <t>사정</t>
         </is>
       </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>"식은땀이 나세요?"</t>
-        </is>
-      </c>
+      <c r="C309" s="2" t="n"/>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>식은땀 있음</t>
-        </is>
-      </c>
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>식은땀 없음</t>
-        </is>
-      </c>
+          <t>의식 명료함</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
+          <t>의식/낙상 (항상)</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -7490,14 +7439,10 @@
           <t>사정</t>
         </is>
       </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>🩺 맥박 불규칙(촉지)</t>
-        </is>
-      </c>
+      <c r="C310" s="2" t="n"/>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
+          <t>Glasgow Coma Scale : (E+V+M)</t>
         </is>
       </c>
       <c r="E310" s="2" t="n"/>
@@ -7505,7 +7450,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
+          <t>의식/낙상 (항상)</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -7513,37 +7458,29 @@
           <t>사정</t>
         </is>
       </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>심전도 리듬 상 부정맥 여부</t>
-        </is>
-      </c>
+      <c r="C311" s="2" t="n"/>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>부정맥 있음</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>부정맥 없음</t>
-        </is>
-      </c>
+          <t>의식수준 저하됨</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B312" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C312" s="2" t="n"/>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
         </is>
       </c>
       <c r="E312" s="2" t="n"/>
@@ -7551,18 +7488,18 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B313" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C313" s="2" t="n"/>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
+          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
         </is>
       </c>
       <c r="E313" s="2" t="n"/>
@@ -7570,18 +7507,18 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B314" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C314" s="2" t="n"/>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>낙상위험</t>
         </is>
       </c>
       <c r="E314" s="2" t="n"/>
@@ -7589,7 +7526,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
+          <t>의식/낙상 (항상)</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -7600,7 +7537,7 @@
       <c r="C315" s="2" t="n"/>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
+          <t>낙상방지 교육함</t>
         </is>
       </c>
       <c r="E315" s="2" t="n"/>
@@ -7608,7 +7545,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
+          <t>의식/낙상 (항상)</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -7619,7 +7556,7 @@
       <c r="C316" s="2" t="n"/>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>부정맥이 있는지 확인함</t>
+          <t>침대 난간을 올려줌</t>
         </is>
       </c>
       <c r="E316" s="2" t="n"/>
@@ -7630,15 +7567,15 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B317" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+      <c r="B317" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C317" s="2" t="n"/>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
+          <t>보호자와 같이 있게 함</t>
         </is>
       </c>
       <c r="E317" s="2" t="n"/>
@@ -7649,165 +7586,13 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B318" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+      <c r="B318" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C318" s="2" t="n"/>
       <c r="D318" s="2" t="inlineStr">
-        <is>
-          <t>Glasgow Coma Scale : (E+V+M)</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="n"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B319" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C319" s="2" t="n"/>
-      <c r="D319" s="2" t="inlineStr">
-        <is>
-          <t>의식수준 저하됨</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="n"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B320" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C320" s="2" t="n"/>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B321" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C321" s="2" t="n"/>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="n"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C322" s="2" t="n"/>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="n"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B323" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C323" s="2" t="n"/>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>낙상방지 교육함</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="n"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B324" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C324" s="2" t="n"/>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>침대 난간을 올려줌</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="n"/>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B325" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C325" s="2" t="n"/>
-      <c r="D325" s="2" t="inlineStr">
-        <is>
-          <t>보호자와 같이 있게 함</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="n"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B326" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C326" s="2" t="n"/>
-      <c r="D326" s="2" t="inlineStr">
         <is>
           <t>보호자 동반하라고 설명함</t>
         </is>

--- a/nursing/통합간호기록_사정진단평가_260626.xlsx
+++ b/nursing/통합간호기록_사정진단평가_260626.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F318"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2855,108 +2855,120 @@
       <c r="E106" s="2" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈중 칼슘(Ca) 높음</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>혈중 calcium 수치 정상 이상임</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="n"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>🩺 부정맥 (불규칙한 맥박)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>부정맥 있음</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>칼륨</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈중 칼슘(Ca) 낮음</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>혈중 calcium 수치 정상 이하임</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="n"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>🩺 근위약·이완성 마비</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>이완성 마비 있음</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>칼륨</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>🩺 tetany 증상 (손발·입 주위 저림, 근육 경련, Chvostek·Trousseau 징후, 반궁긴장, 광과민, 발작 등 신경근 과흥분)</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>tetany 증상 있음</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>tetany 증상 없음(Chvosteck's sign, Trousseau's sign, 반궁긴장, 저린감, perioral numbness, photohypersensitivity, seizure, cramp)</t>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>"설사를 하세요?"</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>설사 있음</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>설사 없음</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>칼슘</t>
+          <t>칼륨</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>🩺 근력 감소 (위약감)</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>근력 감소함</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="n"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>"변비가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>변비 있음</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>변비 없음</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>칼슘</t>
+          <t>칼륨</t>
         </is>
       </c>
     </row>
@@ -2973,20 +2985,15 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>🩺 기면 (자꾸 졸고 처짐)</t>
+          <t>🩺 혈중 칼슘(Ca) 높음</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>lethargy 상태임</t>
+          <t>혈중 calcium 수치 정상 이상임</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>칼슘</t>
-        </is>
-      </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -3001,20 +3008,15 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>"변비가 있으세요?"</t>
+          <t>🩺 혈중 칼슘(Ca) 낮음</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>변비 있음</t>
+          <t>혈중 calcium 수치 정상 이하임</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>칼슘</t>
-        </is>
-      </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -3029,15 +3031,19 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>"배가 아프세요?"</t>
+          <t>🩺 tetany 증상 (손발·입 주위 저림, 근육 경련, Chvostek·Trousseau 징후, 반궁긴장, 광과민, 발작 등 신경근 과흥분)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>복부 통증 있음</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="n"/>
+          <t>tetany 증상 있음</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>tetany 증상 없음(Chvosteck's sign, Trousseau's sign, 반궁긴장, 저린감, perioral numbness, photohypersensitivity, seizure, cramp)</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>칼슘</t>
@@ -3057,12 +3063,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>"소변을 자주 보고 목이 마르세요?"</t>
+          <t>🩺 근력 감소 (위약감)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>다뇨증 있음</t>
+          <t>근력 감소함</t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
@@ -3085,12 +3091,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>🩺 심전도 QT 간격 단축 (고칼슘)</t>
+          <t>🩺 기면 (자꾸 졸고 처짐)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>QT 간격 짧아짐</t>
+          <t>lethargy 상태임</t>
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
@@ -3113,12 +3119,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>🩺 심전도 QT 간격 연장 (저칼슘)</t>
+          <t>"변비가 있으세요?"</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>QT 간격 연장되어 있음</t>
+          <t>변비 있음</t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
@@ -3141,12 +3147,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>🩺 부정맥 (불규칙한 맥박)</t>
+          <t>"배가 아프세요?"</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>부정맥 있음</t>
+          <t>복부 통증 있음</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
@@ -3169,15 +3175,20 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈중 나트륨(Na) 높음</t>
+          <t>"소변을 자주 보고 목이 마르세요?"</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이상임</t>
+          <t>다뇨증 있음</t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -3192,15 +3203,20 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈중 나트륨(Na) 낮음</t>
+          <t>🩺 심전도 QT 간격 단축 (고칼슘)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이하임</t>
+          <t>QT 간격 짧아짐</t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>칼슘</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -3215,18 +3231,18 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>"갈증이 많이 나세요?"</t>
+          <t>🩺 심전도 QT 간격 연장 (저칼슘)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>갈증 있음</t>
+          <t>QT 간격 연장되어 있음</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>나트륨</t>
+          <t>칼슘</t>
         </is>
       </c>
     </row>
@@ -3243,18 +3259,18 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>"메스껍거나 토하세요?"</t>
+          <t>🩺 부정맥 (불규칙한 맥박)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
+          <t>부정맥 있음</t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>나트륨</t>
+          <t>칼슘</t>
         </is>
       </c>
     </row>
@@ -3271,20 +3287,15 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>🩺 의식수준 저하 (처지고 반응이 둔함)</t>
+          <t>🩺 혈중 나트륨(Na) 높음</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>의식수준 저하됨</t>
+          <t>혈중 sodium 수치 정상 이상임</t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -3299,20 +3310,15 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>🩺 경련·발작 보임</t>
+          <t>🩺 혈중 나트륨(Na) 낮음</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>경련 있음</t>
+          <t>혈중 sodium 수치 정상 이하임</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>나트륨</t>
-        </is>
-      </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -3320,18 +3326,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n"/>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>"갈증이 많이 나세요?"</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>갈증 있음</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
@@ -3339,18 +3354,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n"/>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>"메스껍거나 토하세요?"</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -3358,18 +3382,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>🩺 의식수준 저하 (처지고 반응이 둔함)</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 인슐린 투여함</t>
+          <t>의식수준 저하됨</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -3377,18 +3410,27 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n"/>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>🩺 경련·발작 보임</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>경련 있음</t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>나트륨</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -3396,15 +3438,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
@@ -3423,7 +3465,7 @@
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 D50W 을 투여함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
@@ -3434,15 +3476,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>고칼륨혈증</t>
+          <t>처방에 의해 인슐린 투여함</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
@@ -3453,15 +3495,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>hyperkalemia 증상이 있는지 확인함</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
@@ -3480,7 +3522,7 @@
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -3499,7 +3541,7 @@
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 제한하도록 교육함</t>
+          <t>처방에 의해 D50W 을 투여함</t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
@@ -3510,15 +3552,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>혈중 potassium  검사결과 확인함</t>
+          <t>고칼륨혈증</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -3537,7 +3579,7 @@
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
+          <t>hyperkalemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -3548,15 +3590,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -3575,7 +3617,7 @@
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>hypokalemia 증상이 있는지 확인함</t>
+          <t>고칼륨식이 섭취 제한하도록 교육함</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -3613,7 +3655,7 @@
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>처방에 의해 potassium chloride 혼합되지 않은 수액 투여함</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -3624,15 +3666,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 격려함</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -3643,15 +3685,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>고칼슘혈증</t>
+          <t>hypokalemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -3670,7 +3712,7 @@
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>hypercalcemia 증상이 있는지 확인함</t>
+          <t>혈중 potassium  검사결과 확인함</t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -3689,7 +3731,7 @@
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>혈중 calcium 검사결과 확인함</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
@@ -3708,7 +3750,7 @@
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>칼슘 섭취를 제한하도록 함</t>
+          <t>고칼륨식이 섭취 격려함</t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
@@ -3727,7 +3769,7 @@
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>저칼슘혈증</t>
+          <t>고칼슘혈증</t>
         </is>
       </c>
       <c r="E145" s="2" t="n"/>
@@ -3746,7 +3788,7 @@
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>hypocalcemia 증상이 있는지 확인함</t>
+          <t>hypercalcemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E146" s="2" t="n"/>
@@ -3784,7 +3826,7 @@
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Calcium gluconate 를 투여함</t>
+          <t>칼슘 섭취를 제한하도록 함</t>
         </is>
       </c>
       <c r="E148" s="2" t="n"/>
@@ -3803,7 +3845,7 @@
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>고나트륨혈증</t>
+          <t>저칼슘혈증</t>
         </is>
       </c>
       <c r="E149" s="2" t="n"/>
@@ -3822,7 +3864,7 @@
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>hypernatremia의 증상이 있는지 확인함</t>
+          <t>hypocalcemia 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
@@ -3841,7 +3883,7 @@
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>혈중 calcium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
@@ -3852,15 +3894,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>저나트륨혈증</t>
+          <t>처방에 의해 Calcium gluconate 를 투여함</t>
         </is>
       </c>
       <c r="E152" s="2" t="n"/>
@@ -3871,15 +3913,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>hyponatremia 증상이 있는지 확인함</t>
+          <t>고나트륨혈증</t>
         </is>
       </c>
       <c r="E153" s="2" t="n"/>
@@ -3898,7 +3940,7 @@
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>hypernatremia의 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E154" s="2" t="n"/>
@@ -3917,7 +3959,7 @@
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>sodium 섭취를 늘리도록 교육함</t>
+          <t>혈중 sodium 검사결과 확인함</t>
         </is>
       </c>
       <c r="E155" s="2" t="n"/>
@@ -3928,15 +3970,15 @@
           <t>🍬 혈당·전해질</t>
         </is>
       </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
+          <t>저나트륨혈증</t>
         </is>
       </c>
       <c r="E156" s="2" t="n"/>
@@ -3944,110 +3986,78 @@
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>"소변보기 힘드세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>배뇨곤란 있음</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>배뇨곤란 없음</t>
-        </is>
-      </c>
+          <t>hyponatremia 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>"소변이 막힌 느낌이세요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>요정체 있음</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>요정체 없음</t>
-        </is>
-      </c>
+          <t>혈중 sodium 검사결과 확인함</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>잔뇨감 있음</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>잔뇨감 없음</t>
-        </is>
-      </c>
+          <t>sodium 섭취를 늘리도록 교육함</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>🚽 소변</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>"소변에 피가 보이나요?"</t>
-        </is>
-      </c>
+          <t>🍬 혈당·전해질</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>혈뇨 있음</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>혈뇨 없음</t>
-        </is>
-      </c>
+          <t>처방에 의해 Sodium bicarbonate 를 투여함</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n"/>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -4062,15 +4072,19 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>🩺 소변량 감소</t>
+          <t>"소변보기 힘드세요?"</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="n"/>
+          <t>배뇨곤란 있음</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>배뇨곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -4078,18 +4092,26 @@
           <t>🚽 소변</t>
         </is>
       </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>"소변이 막힌 느낌이세요?"</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="n"/>
+          <t>요정체 있음</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>요정체 없음</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
@@ -4097,18 +4119,26 @@
           <t>🚽 소변</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+        </is>
+      </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="n"/>
+          <t>잔뇨감 있음</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>잔뇨감 없음</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -4116,18 +4146,26 @@
           <t>🚽 소변</t>
         </is>
       </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n"/>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>"소변에 피가 보이나요?"</t>
+        </is>
+      </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>단순도뇨 시행함</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="n"/>
+          <t>혈뇨 있음</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>혈뇨 없음</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="18" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
@@ -4135,15 +4173,19 @@
           <t>🚽 소변</t>
         </is>
       </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>🩺 소변량 감소</t>
+        </is>
+      </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="E165" s="2" t="n"/>
@@ -4151,76 +4193,56 @@
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>"귀에서 분비물이 나오세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>귀분비물 있음</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>귀분비물 없음</t>
-        </is>
-      </c>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>"귀울림(이명)이 있으세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>이명 있음</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>이명 없음</t>
-        </is>
-      </c>
+          <t>요정체가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n"/>
     </row>
     <row r="168" ht="36" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>"잘 안 들리세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>청력 이상 있음</t>
+          <t>단순도뇨 시행함</t>
         </is>
       </c>
       <c r="E168" s="2" t="n"/>
@@ -4228,29 +4250,21 @@
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>👂 귀·코·목</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>"코가 막히세요?"</t>
-        </is>
-      </c>
+          <t>🚽 소변</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>코막힘 있음</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>코막힘 없음</t>
-        </is>
-      </c>
+          <t>혈뇨가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -4265,17 +4279,17 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>"콧물이 나세요?"</t>
+          <t>"귀에서 분비물이 나오세요?"</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>콧물 있음</t>
+          <t>귀분비물 있음</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>콧물 없음</t>
+          <t>귀분비물 없음</t>
         </is>
       </c>
     </row>
@@ -4292,17 +4306,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>"삼키기 힘드세요?"</t>
+          <t>"귀울림(이명)이 있으세요?"</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>연하곤란 있음</t>
+          <t>이명 있음</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>연하곤란 없음</t>
+          <t>이명 없음</t>
         </is>
       </c>
     </row>
@@ -4312,15 +4326,19 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>"잘 안 들리세요?"</t>
+        </is>
+      </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>청력 이상 있음</t>
         </is>
       </c>
       <c r="E172" s="2" t="n"/>
@@ -4331,18 +4349,26 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n"/>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>"코가 막히세요?"</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="n"/>
+          <t>코막힘 있음</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>코막힘 없음</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -4350,18 +4376,26 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>"콧물이 나세요?"</t>
+        </is>
+      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>청력장애가 있는지 사정함</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="n"/>
+          <t>콧물 있음</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>콧물 없음</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -4369,128 +4403,102 @@
           <t>👂 귀·코·목</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>"삼키기 힘드세요?"</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="n"/>
+          <t>연하곤란 있음</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>연하곤란 없음</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n"/>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>오심, 구토 없음</t>
-        </is>
-      </c>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>청력장애가 있는지 사정함</t>
         </is>
       </c>
       <c r="E178" s="2" t="n"/>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>💫 어지러워</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+          <t>👂 귀·코·목</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n"/>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
         </is>
       </c>
       <c r="E179" s="2" t="n"/>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -4505,17 +4513,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>감각이상 없음</t>
+          <t>오심, 구토 없음</t>
         </is>
       </c>
     </row>
@@ -4532,17 +4540,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4567,18 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>vertigo 있음</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>vertigo 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -4586,17 +4595,18 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>syncope 있음</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>syncope 없음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -4613,17 +4623,17 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
+          <t>감각이상 있음</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능함</t>
+          <t>감각이상 없음</t>
         </is>
       </c>
     </row>
@@ -4633,18 +4643,26 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n"/>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -4652,18 +4670,26 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n"/>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="n"/>
+          <t>vertigo 있음</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>vertigo 없음</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -4671,18 +4697,26 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n"/>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="n"/>
+          <t>syncope 있음</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>syncope 없음</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -4690,18 +4724,26 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n"/>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -4717,7 +4759,7 @@
       <c r="C189" s="2" t="n"/>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E189" s="2" t="n"/>
@@ -4736,7 +4778,7 @@
       <c r="C190" s="2" t="n"/>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E190" s="2" t="n"/>
@@ -4755,7 +4797,7 @@
       <c r="C191" s="2" t="n"/>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E191" s="2" t="n"/>
@@ -4774,7 +4816,7 @@
       <c r="C192" s="2" t="n"/>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>조직관류 증진 방법에 대해 교육함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E192" s="2" t="n"/>
@@ -4785,15 +4827,15 @@
           <t>💫 어지러워</t>
         </is>
       </c>
-      <c r="B193" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="E193" s="2" t="n"/>
@@ -4801,112 +4843,78 @@
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n"/>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>음독 함 ★</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E194" s="2" t="n"/>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>★칩스확정</t>
-        </is>
-      </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>"토하셨어요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n"/>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>오심, 구토 없음</t>
-        </is>
-      </c>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n"/>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
+          <t>조직관류 증진 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>💊 약먹음</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+          <t>💫 어지러워</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="E197" s="2" t="n"/>
-      <c r="F197" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -4921,18 +4929,18 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>음독 함 ★</t>
         </is>
       </c>
       <c r="E198" s="2" t="n"/>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>입력/선택형</t>
+          <t>★칩스확정</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4957,17 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"토하셨어요?"</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
+          <t>오심, 구토 있음</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>감각이상 없음</t>
+          <t>오심, 구토 없음</t>
         </is>
       </c>
     </row>
@@ -4976,17 +4984,17 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
@@ -5003,17 +5011,18 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -5023,18 +5032,27 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="n"/>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E202" s="2" t="n"/>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -5042,18 +5060,26 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="n"/>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>위세척에 대해 설명함</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="n"/>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -5061,18 +5087,26 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B204" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="n"/>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 해독제를 투여함</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="n"/>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -5080,18 +5114,26 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B205" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="n"/>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -5099,15 +5141,15 @@
           <t>💊 약먹음</t>
         </is>
       </c>
-      <c r="B206" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C206" s="2" t="n"/>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>중독위험</t>
         </is>
       </c>
       <c r="E206" s="2" t="n"/>
@@ -5115,22 +5157,18 @@
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>"부러진 곳(골절)이 있으세요?"</t>
-        </is>
-      </c>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n"/>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>골절 있음</t>
+          <t>위세척에 대해 설명함</t>
         </is>
       </c>
       <c r="E207" s="2" t="n"/>
@@ -5138,83 +5176,59 @@
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>"다친 곳이 붓나요?"</t>
-        </is>
-      </c>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n"/>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>골절부위 edema 있음</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>골절부위 edema 없음</t>
-        </is>
-      </c>
+          <t>처방에 의해 해독제를 투여함</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>"저릿하거나 감각이 이상하세요?"</t>
-        </is>
-      </c>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n"/>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>골절부위 tingling sense 있음</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>골절부위 tingling sense 없음</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>🤕 다쳤어</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
-        </is>
-      </c>
+          <t>💊 약먹음</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n"/>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>찰과상 있음</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>찰과상 없음</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
@@ -5229,19 +5243,15 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>"피가 나나요?"</t>
+          <t>"부러진 곳(골절)이 있으세요?"</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>출혈 있음</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>출혈 없음</t>
-        </is>
-      </c>
+          <t>골절 있음</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n"/>
     </row>
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -5249,18 +5259,26 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="n"/>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>"다친 곳이 붓나요?"</t>
+        </is>
+      </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="n"/>
+          <t>골절부위 edema 있음</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>골절부위 edema 없음</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
@@ -5268,18 +5286,26 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="n"/>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>"저릿하거나 감각이 이상하세요?"</t>
+        </is>
+      </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>골절부위 압박붕대 감아줌</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="n"/>
+          <t>골절부위 tingling sense 있음</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>골절부위 tingling sense 없음</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -5287,18 +5313,26 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B214" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="n"/>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
+        </is>
+      </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>골절부위 올려줌</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="n"/>
+          <t>찰과상 있음</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>찰과상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
@@ -5306,18 +5340,26 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B215" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="n"/>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="n"/>
+          <t>출혈 있음</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>출혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="18" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -5325,15 +5367,15 @@
           <t>🤕 다쳤어</t>
         </is>
       </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C216" s="2" t="n"/>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>sensory motor circulation 확인함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="E216" s="2" t="n"/>
@@ -5341,110 +5383,78 @@
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>"예전보다 잘 안 보이세요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n"/>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>시력감퇴 있음</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>시력감퇴 없음</t>
-        </is>
-      </c>
+          <t>골절부위 압박붕대 감아줌</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>"시야 일부가 가려지세요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n"/>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>시야결손 있음</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>시야결손 없음</t>
-        </is>
-      </c>
+          <t>골절부위 올려줌</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n"/>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>복시 있음</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>복시 없음</t>
-        </is>
-      </c>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>👁️ 눈</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>"눈이 충혈되었나요?"</t>
-        </is>
-      </c>
+          <t>🤕 다쳤어</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n"/>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>결막충혈 있음</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>결막충혈 없음</t>
-        </is>
-      </c>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
@@ -5459,15 +5469,19 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
+          <t>"예전보다 잘 안 보이세요?"</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>이물질 관찰됨</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="n"/>
+          <t>시력감퇴 있음</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>시력감퇴 없음</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -5482,17 +5496,17 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
+          <t>"시야 일부가 가려지세요?"</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>결막출혈 있음</t>
+          <t>시야결손 있음</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>결막출혈 없음</t>
+          <t>시야결손 없음</t>
         </is>
       </c>
     </row>
@@ -5502,18 +5516,26 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="n"/>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+        </is>
+      </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="n"/>
+          <t>복시 있음</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>복시 없음</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -5521,18 +5543,26 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B224" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="n"/>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>"눈이 충혈되었나요?"</t>
+        </is>
+      </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="n"/>
+          <t>결막충혈 있음</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>결막충혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
@@ -5540,15 +5570,19 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B225" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="n"/>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
+        </is>
+      </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>이물질 관찰됨</t>
         </is>
       </c>
       <c r="E225" s="2" t="n"/>
@@ -5559,18 +5593,26 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="n"/>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>안위변화</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="n"/>
+          <t>결막출혈 있음</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>결막출혈 없음</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -5578,15 +5620,15 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C227" s="2" t="n"/>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>이물질 제거함</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
       <c r="E227" s="2" t="n"/>
@@ -5605,7 +5647,7 @@
       <c r="C228" s="2" t="n"/>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>안연고 점안 방법에 대해 교육함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E228" s="2" t="n"/>
@@ -5616,15 +5658,15 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B229" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C229" s="2" t="n"/>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안대 적용함</t>
         </is>
       </c>
       <c r="E229" s="2" t="n"/>
@@ -5635,15 +5677,15 @@
           <t>👁️ 눈</t>
         </is>
       </c>
-      <c r="B230" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C230" s="2" t="n"/>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>안위변화</t>
         </is>
       </c>
       <c r="E230" s="2" t="n"/>
@@ -5662,7 +5704,7 @@
       <c r="C231" s="2" t="n"/>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>이물질 제거함</t>
         </is>
       </c>
       <c r="E231" s="2" t="n"/>
@@ -5670,99 +5712,75 @@
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>"피부가 가려우세요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n"/>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>가려움증 있음</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>가려움증 없음</t>
-        </is>
-      </c>
+          <t>안연고 점안 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>"두드러기가 올라왔나요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n"/>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>urticaria 있음</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>urticaria 없음</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>"물집이 잡혔나요?"</t>
-        </is>
-      </c>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n"/>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>bullae 있음</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>bullae 없음</t>
-        </is>
-      </c>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>🧴 피부</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+          <t>👁️ 눈</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C235" s="2" t="n"/>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E235" s="2" t="n"/>
@@ -5773,18 +5791,26 @@
           <t>🧴 피부</t>
         </is>
       </c>
-      <c r="B236" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="n"/>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="n"/>
+          <t>가려움증 있음</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>가려움증 없음</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
@@ -5792,18 +5818,26 @@
           <t>🧴 피부</t>
         </is>
       </c>
-      <c r="B237" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="n"/>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="n"/>
+          <t>urticaria 있음</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>urticaria 없음</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="36" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -5811,18 +5845,26 @@
           <t>🧴 피부</t>
         </is>
       </c>
-      <c r="B238" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="n"/>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>"물집이 잡혔나요?"</t>
+        </is>
+      </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="n"/>
+          <t>bullae 있음</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>bullae 없음</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="36" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
@@ -5830,15 +5872,15 @@
           <t>🧴 피부</t>
         </is>
       </c>
-      <c r="B239" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C239" s="2" t="n"/>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="E239" s="2" t="n"/>
@@ -5846,112 +5888,78 @@
     <row r="240" ht="36" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n"/>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
+          <t>긁지 않도록 교육함</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B241" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n"/>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E241" s="2" t="n"/>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="242" ht="36" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>🩺 빛 반사</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n"/>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="E242" s="2" t="n"/>
-      <c r="F242" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>🌀 의식이상</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+          <t>🧴 피부</t>
+        </is>
+      </c>
+      <c r="B243" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n"/>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n"/>
     </row>
     <row r="244" ht="36" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -5966,17 +5974,17 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
+          <t>dizziness 있음</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함</t>
+          <t>dizziness 없음</t>
         </is>
       </c>
     </row>
@@ -5993,17 +6001,18 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>obey command 가능함</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n"/>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -6020,17 +6029,18 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+          <t>🩺 빛 반사</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>사람에 대한 지남력 있음</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n"/>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -6047,17 +6057,17 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>섬망 있음</t>
+          <t>감각이상 있음</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>섬망 없음</t>
+          <t>감각이상 없음</t>
         </is>
       </c>
     </row>
@@ -6074,17 +6084,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>환각 있음</t>
+          <t>grasp power 약함</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>환각 없음</t>
+          <t>grasp power 강함</t>
         </is>
       </c>
     </row>
@@ -6101,17 +6111,17 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>🩺 손떨림(flapping tremor)</t>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>flapping tremor 있음</t>
+          <t>obey command 가능하지 않음</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>flapping tremor 없음</t>
+          <t>obey command 가능함</t>
         </is>
       </c>
     </row>
@@ -6121,18 +6131,26 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B250" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="n"/>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+        </is>
+      </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="n"/>
+          <t>사람에 대한 지남력 없음</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>사람에 대한 지남력 있음</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
@@ -6140,18 +6158,26 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="n"/>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+        </is>
+      </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="n"/>
+          <t>섬망 있음</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>섬망 없음</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="18" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -6159,18 +6185,26 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B252" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="n"/>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>"없는 것이 보이거나 들리세요?"</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="n"/>
+          <t>환각 있음</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>환각 없음</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="18" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -6178,18 +6212,26 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B253" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="n"/>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>🩺 손떨림(flapping tremor)</t>
+        </is>
+      </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="n"/>
+          <t>flapping tremor 있음</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>flapping tremor 없음</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -6197,15 +6239,15 @@
           <t>🌀 의식이상</t>
         </is>
       </c>
-      <c r="B254" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C254" s="2" t="n"/>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="E254" s="2" t="n"/>
@@ -6224,7 +6266,7 @@
       <c r="C255" s="2" t="n"/>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="E255" s="2" t="n"/>
@@ -6251,49 +6293,37 @@
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n"/>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>자해나 자살시도를 부인함</t>
-        </is>
-      </c>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B258" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n"/>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>알코올 섭취 양상을 확인함</t>
         </is>
       </c>
       <c r="E258" s="2" t="n"/>
@@ -6301,22 +6331,18 @@
     <row r="259" ht="18" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n"/>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
+          <t>금단 증상을 설명함</t>
         </is>
       </c>
       <c r="E259" s="2" t="n"/>
@@ -6324,29 +6350,21 @@
     <row r="260" ht="18" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>😰 불안·자해</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>🩺 공격적 행동(관찰)</t>
-        </is>
-      </c>
+          <t>🌀 의식이상</t>
+        </is>
+      </c>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n"/>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>공격적 행동함</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>타인에 대한 공격적 행동을 보이지 않음</t>
-        </is>
-      </c>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
@@ -6361,17 +6379,17 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>공황상태 있음</t>
+          <t>구체적 자살계획을 언급함</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>공황상태 없음</t>
+          <t>자해나 자살시도를 부인함</t>
         </is>
       </c>
     </row>
@@ -6381,15 +6399,19 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B262" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="n"/>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>자살을 시도함</t>
         </is>
       </c>
       <c r="E262" s="2" t="n"/>
@@ -6400,15 +6422,19 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B263" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="n"/>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자살 충동 있음</t>
         </is>
       </c>
       <c r="E263" s="2" t="n"/>
@@ -6419,18 +6445,26 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B264" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="n"/>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>🩺 공격적 행동(관찰)</t>
+        </is>
+      </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="n"/>
+          <t>공격적 행동함</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>타인에 대한 공격적 행동을 보이지 않음</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="18" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
@@ -6438,18 +6472,26 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B265" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="n"/>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+        </is>
+      </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="n"/>
+          <t>공황상태 있음</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>공황상태 없음</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="18" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -6457,15 +6499,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B266" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C266" s="2" t="n"/>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>진정시킴</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="E266" s="2" t="n"/>
@@ -6484,7 +6526,7 @@
       <c r="C267" s="2" t="n"/>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E267" s="2" t="n"/>
@@ -6495,15 +6537,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B268" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C268" s="2" t="n"/>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="E268" s="2" t="n"/>
@@ -6514,15 +6556,15 @@
           <t>😰 불안·자해</t>
         </is>
       </c>
-      <c r="B269" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C269" s="2" t="n"/>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
       <c r="E269" s="2" t="n"/>
@@ -6541,7 +6583,7 @@
       <c r="C270" s="2" t="n"/>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>경청해줌</t>
+          <t>진정시킴</t>
         </is>
       </c>
       <c r="E270" s="2" t="n"/>
@@ -6549,111 +6591,78 @@
     <row r="271" ht="18" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n"/>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>감각이상 없음</t>
-        </is>
-      </c>
+          <t>억제대 적용 중임</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n"/>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>grasp power 약함</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>grasp power 강함</t>
-        </is>
-      </c>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n"/>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>국부 마비 있음</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>국부 마비 없음</t>
-        </is>
-      </c>
+          <t>불안을 감소시켜 줌</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>🧠 뇌·신경</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
-        </is>
-      </c>
+          <t>😰 불안·자해</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n"/>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>동공크기 Rt/Lt (mm 입력)</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="E274" s="2" t="n"/>
-      <c r="F274" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="275" ht="18" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -6668,18 +6677,17 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>🩺 동공 상태</t>
+          <t>"한쪽 팔다리가 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="n"/>
-      <c r="F275" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>감각이상 있음</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>감각이상 없음</t>
         </is>
       </c>
     </row>
@@ -6696,18 +6704,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>"손에 힘이 잘 안 들어가세요? 제 손을 한번 꽉 잡아보실래요?"</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>빛 반사: prompt,sluggish,hippus</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="n"/>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>grasp power 강함</t>
         </is>
       </c>
     </row>
@@ -6724,17 +6731,17 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>"한쪽 팔다리가 잘 움직여지지 않으세요?"</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음</t>
+          <t>국부 마비 있음</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>obey command 가능함</t>
+          <t>국부 마비 없음</t>
         </is>
       </c>
     </row>
@@ -6751,17 +6758,18 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>seizure 있음</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>seizure 없음</t>
+          <t>동공크기 Rt/Lt (mm 입력)</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n"/>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -6771,18 +6779,27 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B279" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="n"/>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>🩺 동공 상태</t>
+        </is>
+      </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>동공상태: 동공이 확대됨,동공이 수축됨,동공이 고정되어 있음</t>
         </is>
       </c>
       <c r="E279" s="2" t="n"/>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="36" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -6790,18 +6807,27 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B280" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="n"/>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>빛 반사: prompt,sluggish,hippus</t>
         </is>
       </c>
       <c r="E280" s="2" t="n"/>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="18" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -6809,18 +6835,26 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B281" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="n"/>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="n"/>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>obey command 가능함</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="18" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -6828,18 +6862,26 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B282" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="n"/>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 하신 적이 있으세요?"</t>
+        </is>
+      </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="n"/>
+          <t>seizure 있음</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>seizure 없음</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="18" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -6847,15 +6889,15 @@
           <t>🧠 뇌·신경</t>
         </is>
       </c>
-      <c r="B283" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C283" s="2" t="n"/>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="E283" s="2" t="n"/>
@@ -6874,7 +6916,7 @@
       <c r="C284" s="2" t="n"/>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="E284" s="2" t="n"/>
@@ -6882,78 +6924,56 @@
     <row r="285" ht="18" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B285" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n"/>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>혈압 SBP/DBP (mmHg 입력)</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="E285" s="2" t="n"/>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>입력/선택형</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B286" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n"/>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>dizziness 없음</t>
-        </is>
-      </c>
-      <c r="F286" s="5" t="n"/>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B287" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n"/>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>혈압 상승됨</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="E287" s="2" t="n"/>
@@ -6961,22 +6981,18 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>🩺 혈압(고혈압·저혈압)</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
-        </is>
-      </c>
+          <t>🧠 뇌·신경</t>
+        </is>
+      </c>
+      <c r="B288" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n"/>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E288" s="2" t="n"/>
@@ -6994,17 +7010,18 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>고혈압으로 인한 증상 있음</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>고혈압으로 인한 증상 없음</t>
+          <t>혈압 SBP/DBP (mmHg 입력)</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n"/>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>입력/선택형</t>
         </is>
       </c>
     </row>
@@ -7021,15 +7038,20 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 있음</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="n"/>
+          <t>dizziness 있음</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -7037,15 +7059,19 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B291" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="n"/>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>혈압 상승됨</t>
         </is>
       </c>
       <c r="E291" s="2" t="n"/>
@@ -7056,15 +7082,19 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B292" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C292" s="2" t="n"/>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
+        </is>
+      </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="E292" s="2" t="n"/>
@@ -7075,18 +7105,26 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B293" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="n"/>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
+        </is>
+      </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Non Invasive BP monitor 시작함</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="n"/>
+          <t>고혈압으로 인한 증상 있음</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>고혈압으로 인한 증상 없음</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -7094,15 +7132,19 @@
           <t>🩺 혈압(고혈압·저혈압)</t>
         </is>
       </c>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="n"/>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+        </is>
+      </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>혈압관리 방법에 대해 교육함</t>
+          <t>체위성 저혈압 있음</t>
         </is>
       </c>
       <c r="E294" s="2" t="n"/>
@@ -7121,7 +7163,7 @@
       <c r="C295" s="2" t="n"/>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="E295" s="2" t="n"/>
@@ -7159,7 +7201,7 @@
       <c r="C297" s="2" t="n"/>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="E297" s="2" t="n"/>
@@ -7178,7 +7220,7 @@
       <c r="C298" s="2" t="n"/>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>혈압관리 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="E298" s="2" t="n"/>
@@ -7186,103 +7228,75 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하세요?"</t>
-        </is>
-      </c>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n"/>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 없음</t>
-        </is>
-      </c>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>"가슴이 답답하거나 불편하세요?"</t>
-        </is>
-      </c>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n"/>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>흉부 불편감 없음</t>
-        </is>
-      </c>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>"식은땀이 나세요?"</t>
-        </is>
-      </c>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n"/>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>식은땀 있음</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>식은땀 없음</t>
-        </is>
-      </c>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>❤️ 심장</t>
-        </is>
-      </c>
-      <c r="B302" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>🩺 맥박 불규칙(촉지)</t>
-        </is>
-      </c>
+          <t>🩺 혈압(고혈압·저혈압)</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n"/>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="E302" s="2" t="n"/>
@@ -7300,17 +7314,17 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>심전도 리듬 상 부정맥 여부</t>
+          <t>"숨이 차거나 답답하세요?"</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>부정맥 있음</t>
+          <t>호흡곤란 있음</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>부정맥 없음</t>
+          <t>호흡곤란 없음</t>
         </is>
       </c>
     </row>
@@ -7320,18 +7334,26 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B304" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n"/>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>"가슴이 답답하거나 불편하세요?"</t>
+        </is>
+      </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="n"/>
+          <t>흉부 불편감 있음</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>흉부 불편감 없음</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -7339,18 +7361,26 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B305" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n"/>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>"식은땀이 나세요?"</t>
+        </is>
+      </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="n"/>
+          <t>식은땀 있음</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>식은땀 없음</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -7358,15 +7388,19 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B306" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C306" s="2" t="n"/>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>🩺 맥박 불규칙(촉지)</t>
+        </is>
+      </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>불규칙 맥박 촉지됨</t>
         </is>
       </c>
       <c r="E306" s="2" t="n"/>
@@ -7377,18 +7411,26 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B307" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="n"/>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>심전도 리듬 상 부정맥 여부</t>
+        </is>
+      </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="n"/>
+          <t>부정맥 있음</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>부정맥 없음</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -7396,15 +7438,15 @@
           <t>❤️ 심장</t>
         </is>
       </c>
-      <c r="B308" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C308" s="2" t="n"/>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>부정맥이 있는지 확인함</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
       <c r="E308" s="2" t="n"/>
@@ -7412,18 +7454,18 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B309" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B309" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C309" s="2" t="n"/>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
+          <t>흉부 통증이 있는지 확인함</t>
         </is>
       </c>
       <c r="E309" s="2" t="n"/>
@@ -7431,18 +7473,18 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B310" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B310" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C310" s="2" t="n"/>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Glasgow Coma Scale : (E+V+M)</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="E310" s="2" t="n"/>
@@ -7450,18 +7492,18 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B311" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B311" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C311" s="2" t="n"/>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>의식수준 저하됨</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
       <c r="E311" s="2" t="n"/>
@@ -7469,18 +7511,18 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>의식/낙상 (항상)</t>
-        </is>
-      </c>
-      <c r="B312" s="4" t="inlineStr">
-        <is>
-          <t>사정</t>
+          <t>❤️ 심장</t>
+        </is>
+      </c>
+      <c r="B312" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
         </is>
       </c>
       <c r="C312" s="2" t="n"/>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
+          <t>부정맥이 있는지 확인함</t>
         </is>
       </c>
       <c r="E312" s="2" t="n"/>
@@ -7499,7 +7541,7 @@
       <c r="C313" s="2" t="n"/>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
+          <t>의식 명료함</t>
         </is>
       </c>
       <c r="E313" s="2" t="n"/>
@@ -7510,15 +7552,15 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B314" s="6" t="inlineStr">
-        <is>
-          <t>진단</t>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C314" s="2" t="n"/>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>Glasgow Coma Scale : (E+V+M)</t>
         </is>
       </c>
       <c r="E314" s="2" t="n"/>
@@ -7529,15 +7571,15 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B315" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C315" s="2" t="n"/>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>낙상방지 교육함</t>
+          <t>의식수준 저하됨</t>
         </is>
       </c>
       <c r="E315" s="2" t="n"/>
@@ -7548,15 +7590,15 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B316" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C316" s="2" t="n"/>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>침대 난간을 올려줌</t>
+          <t>시간/장소/사람 에 대한 지남력 있음·없음</t>
         </is>
       </c>
       <c r="E316" s="2" t="n"/>
@@ -7567,15 +7609,15 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B317" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>사정</t>
         </is>
       </c>
       <c r="C317" s="2" t="n"/>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>보호자와 같이 있게 함</t>
+          <t>보호자 환자 옆에 상주하고 있음 / 보호자 동행하지 않음</t>
         </is>
       </c>
       <c r="E317" s="2" t="n"/>
@@ -7586,13 +7628,89 @@
           <t>의식/낙상 (항상)</t>
         </is>
       </c>
-      <c r="B318" s="7" t="inlineStr">
-        <is>
-          <t>평가</t>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>진단</t>
         </is>
       </c>
       <c r="C318" s="2" t="n"/>
       <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n"/>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>낙상방지 교육함</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B320" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n"/>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>침대 난간을 올려줌</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n"/>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>보호자와 같이 있게 함</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>의식/낙상 (항상)</t>
+        </is>
+      </c>
+      <c r="B322" s="7" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n"/>
+      <c r="D322" s="2" t="inlineStr">
         <is>
           <t>보호자 동반하라고 설명함</t>
         </is>

--- a/nursing/통합간호기록_사정진단평가_260626.xlsx
+++ b/nursing/통합간호기록_사정진단평가_260626.xlsx
@@ -1823,6 +1823,11 @@
           <t>객혈 없음</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>객혈</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -1850,6 +1855,11 @@
           <t>토혈 없음</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>토혈</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -1877,6 +1887,11 @@
           <t>혈변 없음</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>흑색혈변</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -1904,6 +1919,11 @@
           <t>흑색변 없음</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>흑색혈변</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -1931,6 +1951,11 @@
           <t>질 출혈 없음</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>질출혈</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -1958,6 +1983,11 @@
           <t>출혈 없음</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -1981,6 +2011,11 @@
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -2004,6 +2039,11 @@
         </is>
       </c>
       <c r="E67" s="2" t="n"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2029,6 +2069,11 @@
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
